--- a/YT_Channel_Assessment.xlsx
+++ b/YT_Channel_Assessment.xlsx
@@ -21,7 +21,7 @@
     <sheet name="Daily Views (raw)" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Video Data'!$A$4:$AC$71</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Video Data'!$A$4:$AH$71</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -178,12 +178,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="AD4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Pulled from each video's public YouTube page in Oct 2026. n/a = page could not be fetched (25 videos, ~15% of views). Comment counts are not shown on public pages in a retrievable form.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AG4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">From YouTube's auto-transcript. "Game commentary only" = the only speech is the in-game commentator, i.e. no creator voice.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="620">
   <si>
     <t xml:space="preserve">YouTube Channel Assessment &amp; New-Channel Strategy</t>
   </si>
@@ -260,7 +284,7 @@
     <t xml:space="preserve">Video Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Every video with 29 columns of stats and calculations, filterable.</t>
+    <t xml:space="preserve">Every video with 34 columns of stats (incl. likes) and calculations, filterable.</t>
   </si>
   <si>
     <t xml:space="preserve">Dig into any single video.</t>
@@ -269,7 +293,7 @@
     <t xml:space="preserve">Market Research</t>
   </si>
   <si>
-    <t xml:space="preserve">14 research findings on Shorts, CTR, AI, gaming and monetization in 2026, with sources.</t>
+    <t xml:space="preserve">15 research findings on Shorts, CTR, AI, gaming and monetization in 2026, with sources.</t>
   </si>
   <si>
     <t xml:space="preserve">Understand the 2026 landscape.</t>
@@ -365,7 +389,7 @@
     <t xml:space="preserve">A video that keeps getting views for months, not just launch week.</t>
   </si>
   <si>
-    <t xml:space="preserve">Method note: data was pulled from the YouTube Studio export you shared via Google Sheets (Table data, Chart data, Totals). Comments, likes and retention were not in that export; see "Data Gaps &amp; How-To".</t>
+    <t xml:space="preserve">Method note: data was pulled from the YouTube Studio export you shared via Google Sheets (Table data, Chart data, Totals). Likes, descriptions and audio type were added from each video's public YouTube page. Comments, shares and retention were not obtainable; see "Data Gaps &amp; How-To".</t>
   </si>
   <si>
     <t xml:space="preserve">Old Channel Performance: Dashboard</t>
@@ -452,12 +476,15 @@
     <t xml:space="preserve">Skewed by one hit; see median.</t>
   </si>
   <si>
-    <t xml:space="preserve">Benchmarks: CTR 6% = solid (typical 4–6%, gaming ~8.5%, focus-digital/subsub 2026). Subs/1K: long-form 2.27, Shorts 1.69 (Galloway). Shorts AVD 15s = a well-held 15–35s Short. Top-video share 15% = a healthy, non-hit-dependent channel. Uploads: ~1 per week minimum. Blue numbers are editable benchmarks.</t>
+    <t xml:space="preserve">Likes per 1K views</t>
   </si>
   <si>
     <t xml:space="preserve">About the Shorts benchmark (1.7). Long-form benchmark is ~2.3.</t>
   </si>
   <si>
+    <t xml:space="preserve">Benchmarks: CTR 6% = solid (typical 4–6%, gaming ~8.5%, focus-digital/subsub 2026). Subs/1K: long-form 2.27, Shorts 1.69 (Galloway). Shorts AVD 15s = a well-held 15–35s Short. Top-video share 15% = a healthy, non-hit-dependent channel. Uploads: ~1 per week minimum. Likes: typical 10–30 per 1K views (upgrowth.in). Blue numbers are editable benchmarks.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Median views per video</t>
   </si>
   <si>
@@ -482,6 +509,9 @@
     <t xml:space="preserve">Six videos = most of your views. The other 61 = the rest.</t>
   </si>
   <si>
+    <t xml:space="preserve">From public video pages (42 videos, 85% of views). Typical is 10–30. Viewers watched but didn't react.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Top 10 videos</t>
   </si>
   <si>
@@ -497,7 +527,7 @@
     <t xml:space="preserve">Theme</t>
   </si>
   <si>
-    <t xml:space="preserve">10 key findings (the "so what")</t>
+    <t xml:space="preserve">11 key findings (the "so what")</t>
   </si>
   <si>
     <t xml:space="preserve">1. Hit-driven channel</t>
@@ -554,7 +584,13 @@
     <t xml:space="preserve">About 1.8 subs per 1K views (51 subs from 29K views). Viewers had no reason to subscribe: no series, no voice, no recurring promise.</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Monetization rules now reward long-form</t>
+    <t xml:space="preserve">10. Reach ≠ resonance (likes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umpire-drama clips got the most views but only ~2.6 likes per 1K views. Your older gameplay videos earned 10–40 per 1K. Clips of 31–60 seconds earned 15.8 likes per 1K vs 2.4 for clips of 10 seconds or less. Feed viewers watched a 4-second loop and swiped on, with no voice of yours to connect with.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Monetization rules now reward long-form</t>
   </si>
   <si>
     <t xml:space="preserve">2027 YPP rules: 1,000 subs plus 8,000 long-form watch hours (or 20M Shorts views in 90 days). Your old pace would never get there, so the new channel needs long-form from day one.</t>
@@ -629,7 +665,7 @@
     <t xml:space="preserve">Make Shorts 15–35 seconds with a setup, the moment, a replay or reaction, and a payoff. Stop posting 3–5 second clips.</t>
   </si>
   <si>
-    <t xml:space="preserve">Your 2025–26 clips averaged 4.4 seconds of watch per view. Watch time fell about 75% vs the old era and subs per 1K views collapsed. Ultra-short loops inflate raw views but build nothing.</t>
+    <t xml:space="preserve">Your 2025–26 clips averaged 4.4 seconds of watch per view. Watch time fell about 75% vs the old era and subs per 1K views collapsed. Ultra-short loops inflate raw views but build nothing. Likes tell the same story: 31–60s clips earned 15.8 likes per 1K vs 2.4 for ≤10s.</t>
   </si>
   <si>
     <t xml:space="preserve">Avg view duration ≥ 12 seconds; avg % watched ≥ 80%</t>
@@ -734,18 +770,21 @@
     <t xml:space="preserve">YouTube's 2025/2026 inauthentic-content policy targets templated, low-effort content. Your clip uploads had no persona, so few viewers subscribed.</t>
   </si>
   <si>
+    <t xml:space="preserve">Likes ≥ 20 per 1K views; comments ≥ 5 per 1K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engagement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End every Short with a question ("OUT or NOT OUT? Comment 👇") and pin a comment. Reply to every comment in the first hour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your outrage and question titles were your best performers. Comments and replies are satisfaction signals.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Comments per 1K views ≥ 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Engagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End every Short with a question ("OUT or NOT OUT? Comment 👇") and pin a comment. Reply to every comment in the first hour.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your outrage and question titles were your best performers. Comments and replies are satisfaction signals.</t>
-  </si>
-  <si>
     <t xml:space="preserve">AI workflow</t>
   </si>
   <si>
@@ -941,7 +980,7 @@
     <t xml:space="preserve">DOUBLE DOWN</t>
   </si>
   <si>
-    <t xml:space="preserve">Your proven format. 4 of your 5 biggest videos. Outrage + a question ("How is that NOT OUT?!") earns the click and the comments. But the median is low: most uploads got under 100 views. The winners had a clear "wait, what?!" moment in the first second.</t>
+    <t xml:space="preserve">Your proven format. 4 of your 5 biggest videos. Outrage + a question ("How is that NOT OUT?!") earns the click and the comments. But the median is low: most uploads got under 100 views. The winners had a clear "wait, what?!" moment in the first second. Warning: only ~2.6 likes per 1K views. People watched but didn't react, so add your own reaction and a question.</t>
   </si>
   <si>
     <t xml:space="preserve">Cricket: Gameplay &amp; Moments</t>
@@ -1088,7 +1127,19 @@
     <t xml:space="preserve">💡 ≤10-second clips have the highest average views (mostly thanks to your 3-second viral hit) because they loop. But viewers stayed only ~3 seconds and subs per 1K views were lowest. 11–60 second clips earned 2x the subscribers per view. Test 15–35 second Shorts with a setup, the moment, and a payoff or reaction.</t>
   </si>
   <si>
-    <t xml:space="preserve">7. Upload weekday (low confidence)</t>
+    <t xml:space="preserve">7. Audio: what viewers hear (videos with a fetched page)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game commentary only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music / no speech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💡 None of your fetched videos has YOUR voice. The only speech is the in-game commentator ("Let's take a look at that in slow motion"). Viewers had no person to connect with, which is a big reason subs and likes stayed low. Adding your own commentary or reactions is the cheapest upgrade available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Upload weekday (low confidence)</t>
   </si>
   <si>
     <t xml:space="preserve">Mon</t>
@@ -1295,6 +1346,18 @@
     <t xml:space="preserve">Watch</t>
   </si>
   <si>
+    <t xml:space="preserve">Likes (public page)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description length (chars)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audio on video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Views where likes known</t>
+  </si>
+  <si>
     <t xml:space="preserve">9srtvMvNdHE</t>
   </si>
   <si>
@@ -1322,6 +1385,9 @@
     <t xml:space="preserve">CRICKET 07 2011 THE TENTH WORLD WAR!</t>
   </si>
   <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
     <t xml:space="preserve">dG3Y_PJcRac</t>
   </si>
   <si>
@@ -1883,6 +1949,21 @@
     <t xml:space="preserve">hashtagtools.io/blog/youtube-shorts-hashtags-title-vs-description-2026 ; tubecore.xpanddigital.io/blog/youtube-hashtags-guide</t>
   </si>
   <si>
+    <t xml:space="preserve">Engagement benchmarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typical like rate is 1–3% of views (10–30 likes per 1K). Some tools put Shorts at 3–5%. CreatorDB finds likes per view are similar for Shorts and long-form; the bigger gap is in comments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your channel averaged ~5 likes per 1K, and your umpire clips only ~2.6. Raising likes and comments is mainly about giving people something to react to: your voice, a question, a debate ("OUT or NOT OUT?").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicative (tool vendors)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrowth.in/social-media-tools/youtube-engagement-rate-calculator ; creatordb.app/research/youtube-view-count-change</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trends</t>
   </si>
   <si>
@@ -1913,13 +1994,13 @@
     <t xml:space="preserve">How to export it from YouTube Studio</t>
   </si>
   <si>
-    <t xml:space="preserve">Comments, likes, shares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engagement signals; tells you which videos sparked conversation (your outrage titles probably did).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Studio → Analytics → Advanced mode → Content tab → column picker → add Comments added, Likes, Shares. Export → Google Sheets.</t>
+    <t xml:space="preserve">Comments &amp; shares (likes now included)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likes were pulled from your public video pages for 42 of 67 videos (85% of views); see Video Data columns AD–AE. Comment and share counts are not exposed in a fetchable form, and the one page that showed them read "0 Comments". These are the last engagement signals missing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio → Analytics → Advanced mode → Content tab → column picker → add Comments added, Shares, Likes. Export → Google Sheets, then share the link. They plug straight into the Video Data tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Average % viewed &amp; retention curve</t>
@@ -3895,11 +3976,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="52896139"/>
-        <c:axId val="69230306"/>
+        <c:axId val="81489220"/>
+        <c:axId val="30460172"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52896139"/>
+        <c:axId val="81489220"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3931,7 +4012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69230306"/>
+        <c:crossAx val="30460172"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3939,7 +4020,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69230306"/>
+        <c:axId val="30460172"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3981,7 +4062,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52896139"/>
+        <c:crossAx val="81489220"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4439,11 +4520,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="36109339"/>
-        <c:axId val="31682778"/>
+        <c:axId val="15866268"/>
+        <c:axId val="56316284"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="36109339"/>
+        <c:axId val="15866268"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4475,7 +4556,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31682778"/>
+        <c:crossAx val="56316284"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4483,7 +4564,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31682778"/>
+        <c:axId val="56316284"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4525,7 +4606,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36109339"/>
+        <c:crossAx val="15866268"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4709,11 +4790,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71265558"/>
-        <c:axId val="80443612"/>
+        <c:axId val="2269866"/>
+        <c:axId val="42866713"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71265558"/>
+        <c:axId val="2269866"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4745,7 +4826,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80443612"/>
+        <c:crossAx val="42866713"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4753,7 +4834,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80443612"/>
+        <c:axId val="42866713"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4829,7 +4910,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71265558"/>
+        <c:crossAx val="2269866"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5013,11 +5094,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="85290859"/>
-        <c:axId val="2376364"/>
+        <c:axId val="1158945"/>
+        <c:axId val="89095803"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85290859"/>
+        <c:axId val="1158945"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -5049,7 +5130,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2376364"/>
+        <c:crossAx val="89095803"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5057,7 +5138,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2376364"/>
+        <c:axId val="89095803"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5099,7 +5180,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85290859"/>
+        <c:crossAx val="1158945"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5557,8 +5638,8 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="31387901"/>
-        <c:axId val="93173357"/>
+        <c:axId val="82581212"/>
+        <c:axId val="49344323"/>
       </c:lineChart>
       <c:barChart>
         <c:barDir val="col"/>
@@ -5941,11 +6022,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57745454"/>
-        <c:axId val="48610523"/>
+        <c:axId val="23122174"/>
+        <c:axId val="20920688"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="31387901"/>
+        <c:axId val="82581212"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5977,7 +6058,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93173357"/>
+        <c:crossAx val="49344323"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5985,7 +6066,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93173357"/>
+        <c:axId val="49344323"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6061,12 +6142,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31387901"/>
+        <c:crossAx val="82581212"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="57745454"/>
+        <c:axId val="23122174"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6098,7 +6179,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48610523"/>
+        <c:crossAx val="20920688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6106,7 +6187,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48610523"/>
+        <c:axId val="20920688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6172,7 +6253,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57745454"/>
+        <c:crossAx val="23122174"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6460,11 +6541,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="66324077"/>
-        <c:axId val="23704331"/>
+        <c:axId val="52290507"/>
+        <c:axId val="42863057"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66324077"/>
+        <c:axId val="52290507"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6496,7 +6577,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23704331"/>
+        <c:crossAx val="42863057"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6504,7 +6585,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23704331"/>
+        <c:axId val="42863057"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6546,7 +6627,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66324077"/>
+        <c:crossAx val="52290507"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6611,13 +6692,13 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>256320</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>174600</xdr:rowOff>
+      <xdr:rowOff>174960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6625,7 +6706,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="14074200" y="6305400"/>
+        <a:off x="14074200" y="6496200"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6679,8 +6760,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>1827720</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1122840</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>21960</xdr:rowOff>
     </xdr:to>
@@ -7294,105 +7375,105 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>572</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="42" t="s">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>578</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="42" t="s">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="42" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="42" t="s">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="42" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>593</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="42" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>596</v>
+        <v>615</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="62" t="s">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="B13" s="62"/>
       <c r="C13" s="62"/>
@@ -7426,20 +7507,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>598</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>599</v>
+        <v>618</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22907,7 +22988,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -23123,12 +23204,20 @@
       <c r="D12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
+      <c r="G12" s="24" t="n">
+        <f aca="false">C18</f>
+        <v>5.34275106402246</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" s="20" t="str">
+        <f aca="false">IF(G12&gt;=H12,"✅ On track",IF(G12&gt;=10,"🟡 Close","🔴 Fix"))</f>
+        <v>🔴 Fix</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="15" t="s">
@@ -23141,21 +23230,23 @@
       <c r="D13" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="16"/>
+      <c r="F13" s="16" t="s">
+        <v>91</v>
+      </c>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" s="32" t="n">
         <f aca="false">MEDIAN('Video Data'!$K$5:$K$71)</f>
         <v>129</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
@@ -23164,60 +23255,84 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" s="33" t="n">
         <f aca="false">C7*3600/C6</f>
         <v>10.4378928522242</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>94</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" s="34" t="n">
         <f aca="false">'Video Data'!K5/C6</f>
         <v>0.296412339898086</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="34" t="n">
         <f aca="false">SUM('Video Data'!K5:K10)/C6</f>
         <v>0.573509158518111</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <f aca="false">SUM('Video Data'!$AD$5:$AD$71)/SUM('Video Data'!$AH$5:$AH$71)*1000</f>
+        <v>5.34275106402246</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23432,15 +23547,15 @@
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D34" s="40"/>
       <c r="E34" s="40"/>
@@ -23451,10 +23566,10 @@
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D35" s="40"/>
       <c r="E35" s="40"/>
@@ -23465,10 +23580,10 @@
     </row>
     <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D36" s="40"/>
       <c r="E36" s="40"/>
@@ -23479,10 +23594,10 @@
     </row>
     <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="39" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D37" s="40"/>
       <c r="E37" s="40"/>
@@ -23493,10 +23608,10 @@
     </row>
     <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="39" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D38" s="40"/>
       <c r="E38" s="40"/>
@@ -23507,10 +23622,10 @@
     </row>
     <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="39" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D39" s="40"/>
       <c r="E39" s="40"/>
@@ -23521,10 +23636,10 @@
     </row>
     <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="39" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D40" s="40"/>
       <c r="E40" s="40"/>
@@ -23535,10 +23650,10 @@
     </row>
     <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C41" s="40" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D41" s="40"/>
       <c r="E41" s="40"/>
@@ -23549,10 +23664,10 @@
     </row>
     <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="39" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C42" s="40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D42" s="40"/>
       <c r="E42" s="40"/>
@@ -23563,10 +23678,10 @@
     </row>
     <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D43" s="40"/>
       <c r="E43" s="40"/>
@@ -23575,14 +23690,28 @@
       <c r="H43" s="40"/>
       <c r="I43" s="40"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="41" t="s">
-        <v>125</v>
+    <row r="44" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="41" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="F12:I14"/>
+  <mergeCells count="12">
+    <mergeCell ref="F13:I17"/>
     <mergeCell ref="C34:I34"/>
     <mergeCell ref="C35:I35"/>
     <mergeCell ref="C36:I36"/>
@@ -23593,8 +23722,9 @@
     <mergeCell ref="C41:I41"/>
     <mergeCell ref="C42:I42"/>
     <mergeCell ref="C43:I43"/>
+    <mergeCell ref="C44:I44"/>
   </mergeCells>
-  <conditionalFormatting sqref="I6:I11">
+  <conditionalFormatting sqref="I6:I12">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEFT(I6,1)="✅"</formula>
     </cfRule>
@@ -23614,7 +23744,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{926BA818-F1A9-47FD-9E71-2100B57F11AD}</x14:id>
+          <x14:id>{479AD0F0-658B-4510-87BB-29B079E8F1FC}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23643,7 +23773,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{926BA818-F1A9-47FD-9E71-2100B57F11AD}">
+          <x14:cfRule type="dataBar" id="{479AD0F0-658B-4510-87BB-29B079E8F1FC}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23681,35 +23811,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>70</v>
@@ -23720,25 +23850,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23746,25 +23876,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F6" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23772,25 +23902,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23798,25 +23928,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23824,25 +23954,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23850,25 +23980,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23876,25 +24006,25 @@
         <v>7</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23902,25 +24032,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23928,25 +24058,25 @@
         <v>9</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C13" s="42" t="s">
         <v>58</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23954,25 +24084,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23980,25 +24110,25 @@
         <v>11</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24006,25 +24136,25 @@
         <v>12</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24032,25 +24162,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24058,25 +24188,25 @@
         <v>14</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24084,25 +24214,25 @@
         <v>15</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24110,25 +24240,25 @@
         <v>16</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24136,39 +24266,39 @@
         <v>17</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="43" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C25" s="43"/>
       <c r="D25" s="40" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E25" s="40"/>
       <c r="F25" s="40"/>
@@ -24177,11 +24307,11 @@
     </row>
     <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="43" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C26" s="43"/>
       <c r="D26" s="40" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E26" s="40"/>
       <c r="F26" s="40"/>
@@ -24190,11 +24320,11 @@
     </row>
     <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="43" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C27" s="43"/>
       <c r="D27" s="40" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E27" s="40"/>
       <c r="F27" s="40"/>
@@ -24203,7 +24333,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24213,20 +24343,20 @@
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="44" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="38" t="n">
@@ -24237,7 +24367,7 @@
         <v>0.07</v>
       </c>
       <c r="F31" s="40" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G31" s="40"/>
       <c r="H31" s="40"/>
@@ -24255,7 +24385,7 @@
         <v>12</v>
       </c>
       <c r="F32" s="40" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G32" s="40"/>
       <c r="H32" s="40"/>
@@ -24273,14 +24403,14 @@
         <v>3</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G33" s="40"/>
       <c r="H33" s="40"/>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="44" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C34" s="44"/>
       <c r="D34" s="46" t="n">
@@ -24291,14 +24421,14 @@
         <v>20</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G34" s="40"/>
       <c r="H34" s="40"/>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="44" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C35" s="44"/>
       <c r="D35" s="37" t="n">
@@ -24309,14 +24439,14 @@
         <v>4000</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G35" s="40"/>
       <c r="H35" s="40"/>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="44" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C36" s="44"/>
       <c r="D36" s="49" t="n">
@@ -24327,14 +24457,14 @@
         <v>0.9</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G36" s="40"/>
       <c r="H36" s="40"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="51" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -24403,7 +24533,7 @@
     <tabColor rgb="FF0F766E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -24416,48 +24546,48 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>54</v>
@@ -24466,18 +24596,21 @@
         <v>46</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>248</v>
+        <v>89</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="42" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B5" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$H$5:$H$71,A5)</f>
@@ -24523,16 +24656,20 @@
         <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A5,'Video Data'!$S$5:$S$71)/K5,0)</f>
         <v>0.0690660797747828</v>
       </c>
-      <c r="M5" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>252</v>
+      <c r="M5" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A5,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$H$5:$H$71,A5,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>2.55383365256254</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="42" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B6" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$H$5:$H$71,A6)</f>
@@ -24578,16 +24715,20 @@
         <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A6,'Video Data'!$S$5:$S$71)/K6,0)</f>
         <v>0.0467013357805649</v>
       </c>
-      <c r="M6" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>255</v>
+      <c r="M6" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A6,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$H$5:$H$71,A6,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>14.5882352941176</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="42" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$H$5:$H$71,A7)</f>
@@ -24633,16 +24774,20 @@
         <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A7,'Video Data'!$S$5:$S$71)/K7,0)</f>
         <v>0.00865301413325642</v>
       </c>
-      <c r="M7" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>258</v>
+      <c r="M7" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A7,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$H$5:$H$71,A7,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>14.6935348446683</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$H$5:$H$71,A8)</f>
@@ -24688,16 +24833,20 @@
         <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A8,'Video Data'!$S$5:$S$71)/K8,0)</f>
         <v>0.0452492617682821</v>
       </c>
-      <c r="M8" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>261</v>
+      <c r="M8" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A8,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$H$5:$H$71,A8,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>10.2564102564103</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="42" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B9" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$H$5:$H$71,A9)</f>
@@ -24743,16 +24892,20 @@
         <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A9,'Video Data'!$S$5:$S$71)/K9,0)</f>
         <v>0.0189473684210526</v>
       </c>
-      <c r="M9" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>263</v>
+      <c r="M9" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A9,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$H$5:$H$71,A9,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>39.4736842105263</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="42" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B10" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$H$5:$H$71,A10)</f>
@@ -24798,16 +24951,20 @@
         <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A10,'Video Data'!$S$5:$S$71)/K10,0)</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="M10" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>266</v>
+      <c r="M10" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$H$5:$H$71,A10,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$H$5:$H$71,A10,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B11" s="54" t="n">
         <f aca="false">SUM(B5:B10)</f>
@@ -24853,9 +25010,13 @@
         <f aca="false">IFERROR(SUM('Video Data'!$S$5:$S$71)/K11,0)</f>
         <v>0.0582166731007579</v>
       </c>
+      <c r="M11" s="57" t="n">
+        <f aca="false">IFERROR(SUM('Video Data'!$AD$5:$AD$71)/SUM('Video Data'!$AH$5:$AH$71)*1000,0)</f>
+        <v>5.34275106402246</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M5:M10">
+  <conditionalFormatting sqref="N5:N10">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"DOUBLE DOWN"</formula>
     </cfRule>
@@ -24881,7 +25042,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{877A6AB5-CA60-481E-8CBD-F2D1E32C3941}</x14:id>
+          <x14:id>{FF759266-F7F2-4751-BA41-C01D4B96B16D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24909,8 +25070,19 @@
       <formula>AND(ISNUMBER(L5),L5&lt;0.04)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M10">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(M5),M5&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(M5),AND(M5&gt;=10,M5&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(M5),M5&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H5:H10">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -24933,7 +25105,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{877A6AB5-CA60-481E-8CBD-F2D1E32C3941}">
+          <x14:cfRule type="dataBar" id="{FF759266-F7F2-4751-BA41-C01D4B96B16D}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -24957,7 +25129,7 @@
     <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -24969,41 +25141,42 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="60" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>54</v>
@@ -25012,15 +25185,18 @@
         <v>46</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="61" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B6" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$G$5:$G$71,A6)</f>
@@ -25058,10 +25234,14 @@
         <f aca="false">IF(B6&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K6" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$G$5:$G$71,A6,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$G$5:$G$71,A6,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>5.32592862345229</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="61" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$G$5:$G$71,A7)</f>
@@ -25099,10 +25279,14 @@
         <f aca="false">IF(B7&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K7" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$G$5:$G$71,A7,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$G$5:$G$71,A7,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>8.47457627118644</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="62" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B8" s="62"/>
       <c r="C8" s="62"/>
@@ -25113,30 +25297,31 @@
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
       <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="60" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>54</v>
@@ -25145,15 +25330,18 @@
         <v>46</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="61" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B12" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$I$5:$I$71,A12)</f>
@@ -25191,10 +25379,14 @@
         <f aca="false">IF(B12&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K12" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$I$5:$I$71,A12,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$I$5:$I$71,A12,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>7.23048176131286</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="61" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B13" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$I$5:$I$71,A13)</f>
@@ -25232,10 +25424,14 @@
         <f aca="false">IF(B13&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K13" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$I$5:$I$71,A13,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$I$5:$I$71,A13,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>2.96614503426409</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="62" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B14" s="62"/>
       <c r="C14" s="62"/>
@@ -25246,30 +25442,31 @@
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
       <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>54</v>
@@ -25278,15 +25475,18 @@
         <v>46</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="61" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B18" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$Y$5:$Y$71,A18)</f>
@@ -25324,10 +25524,14 @@
         <f aca="false">IF(B18&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K18" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$Y$5:$Y$71,A18,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$Y$5:$Y$71,A18,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>3.23295216428187</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="61" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B19" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$Y$5:$Y$71,A19)</f>
@@ -25365,10 +25569,14 @@
         <f aca="false">IF(B19&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K19" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$Y$5:$Y$71,A19,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$Y$5:$Y$71,A19,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>4.23370025402202</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="61" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B20" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$Y$5:$Y$71,A20)</f>
@@ -25406,10 +25614,14 @@
         <f aca="false">IF(B20&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K20" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$Y$5:$Y$71,A20,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$Y$5:$Y$71,A20,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>15.984015984016</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="61" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B21" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$Y$5:$Y$71,A21)</f>
@@ -25447,10 +25659,14 @@
         <f aca="false">IF(B21&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K21" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$Y$5:$Y$71,A21,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$Y$5:$Y$71,A21,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>21.5897939156035</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="62" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B22" s="62"/>
       <c r="C22" s="62"/>
@@ -25461,30 +25677,31 @@
       <c r="H22" s="62"/>
       <c r="I22" s="62"/>
       <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="60" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>54</v>
@@ -25493,15 +25710,18 @@
         <v>46</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="61" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B26" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$W$5:$W$71,A26)</f>
@@ -25539,10 +25759,14 @@
         <f aca="false">IF(B26&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K26" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$W$5:$W$71,A26,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$W$5:$W$71,A26,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>1.96592398427261</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="61" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B27" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$W$5:$W$71,A27)</f>
@@ -25580,10 +25804,14 @@
         <f aca="false">IF(B27&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K27" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$W$5:$W$71,A27,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$W$5:$W$71,A27,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>5.88420720815383</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="62" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B28" s="62"/>
       <c r="C28" s="62"/>
@@ -25594,30 +25822,31 @@
       <c r="H28" s="62"/>
       <c r="I28" s="62"/>
       <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="60" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>54</v>
@@ -25626,15 +25855,18 @@
         <v>46</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="61" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B32" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$Z$5:$Z$71,A32)</f>
@@ -25672,10 +25904,14 @@
         <f aca="false">IF(B32&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K32" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$Z$5:$Z$71,A32,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$Z$5:$Z$71,A32,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>1.5547703180212</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="61" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B33" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$Z$5:$Z$71,A33)</f>
@@ -25713,10 +25949,14 @@
         <f aca="false">IF(B33&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K33" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$Z$5:$Z$71,A33,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$Z$5:$Z$71,A33,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>4.32120993878286</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="61" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B34" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$Z$5:$Z$71,A34)</f>
@@ -25754,10 +25994,14 @@
         <f aca="false">IF(B34&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K34" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$Z$5:$Z$71,A34,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$Z$5:$Z$71,A34,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>15.1165769920574</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="62" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B35" s="62"/>
       <c r="C35" s="62"/>
@@ -25768,30 +26012,31 @@
       <c r="H35" s="62"/>
       <c r="I35" s="62"/>
       <c r="J35" s="62"/>
+      <c r="K35" s="62"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="60" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>54</v>
@@ -25800,15 +26045,18 @@
         <v>46</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="61" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B39" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$AA$5:$AA$71,A39)</f>
@@ -25846,10 +26094,14 @@
         <f aca="false">IF(B39&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K39" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AA$5:$AA$71,A39,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$AA$5:$AA$71,A39,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>2.39683876400855</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="61" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B40" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$AA$5:$AA$71,A40)</f>
@@ -25887,10 +26139,14 @@
         <f aca="false">IF(B40&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K40" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AA$5:$AA$71,A40,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$AA$5:$AA$71,A40,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>6.54582074521652</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="61" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B41" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$AA$5:$AA$71,A41)</f>
@@ -25928,10 +26184,14 @@
         <f aca="false">IF(B41&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K41" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AA$5:$AA$71,A41,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$AA$5:$AA$71,A41,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>15.8473479948254</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="61" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B42" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$AA$5:$AA$71,A42)</f>
@@ -25969,10 +26229,14 @@
         <f aca="false">IF(B42&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K42" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AA$5:$AA$71,A42,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$AA$5:$AA$71,A42,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>12.388162422574</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="61" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B43" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$AA$5:$AA$71,A43)</f>
@@ -26010,10 +26274,14 @@
         <f aca="false">IF(B43&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K43" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AA$5:$AA$71,A43,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$AA$5:$AA$71,A43,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>8.47457627118644</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="62" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B44" s="62"/>
       <c r="C44" s="62"/>
@@ -26024,30 +26292,31 @@
       <c r="H44" s="62"/>
       <c r="I44" s="62"/>
       <c r="J44" s="62"/>
+      <c r="K44" s="62"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="60" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>54</v>
@@ -26056,322 +26325,500 @@
         <v>46</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="61" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B48" s="35" t="n">
-        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A48)</f>
-        <v>8</v>
+        <f aca="false">COUNTIF('Video Data'!$AG$5:$AG$71,A48)</f>
+        <v>19</v>
       </c>
       <c r="C48" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A48,'Video Data'!$K$5:$K$71)</f>
-        <v>790</v>
+        <f aca="false">SUMIF('Video Data'!$AG$5:$AG$71,A48,'Video Data'!$K$5:$K$71)</f>
+        <v>15237</v>
       </c>
       <c r="D48" s="37" t="n">
         <f aca="false">IFERROR(C48/B48,0)</f>
-        <v>98.75</v>
+        <v>801.947368421053</v>
       </c>
       <c r="E48" s="46" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A48,'Video Data'!$L$5:$L$71)</f>
-        <v>7.6445</v>
+        <f aca="false">SUMIF('Video Data'!$AG$5:$AG$71,A48,'Video Data'!$L$5:$L$71)</f>
+        <v>18.9006</v>
       </c>
       <c r="F48" s="46" t="n">
         <f aca="false">IFERROR(E48*3600/C48,0)</f>
-        <v>34.8356962025317</v>
+        <v>4.46558771411695</v>
       </c>
       <c r="G48" s="52" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A48,'Video Data'!$O$5:$O$71)/C48*1000,0)</f>
-        <v>1.26582278481013</v>
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AG$5:$AG$71,A48,'Video Data'!$O$5:$O$71)/C48*1000,0)</f>
+        <v>0.721926888495111</v>
       </c>
       <c r="H48" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A48,'Video Data'!$Q$5:$Q$71)</f>
-        <v>8549</v>
+        <f aca="false">SUMIF('Video Data'!$AG$5:$AG$71,A48,'Video Data'!$Q$5:$Q$71)</f>
+        <v>146723</v>
       </c>
       <c r="I48" s="53" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A48,'Video Data'!$S$5:$S$71)/H48,0)</f>
-        <v>0.0426950520528717</v>
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AG$5:$AG$71,A48,'Video Data'!$S$5:$S$71)/H48,0)</f>
+        <v>0.063984515038542</v>
       </c>
       <c r="J48" s="36" t="str">
         <f aca="false">IF(B48&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
+      <c r="K48" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AG$5:$AG$71,A48,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$AG$5:$AG$71,A48,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>3.60963444247555</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="61" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B49" s="35" t="n">
-        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A49)</f>
-        <v>11</v>
+        <f aca="false">COUNTIF('Video Data'!$AG$5:$AG$71,A49)</f>
+        <v>23</v>
       </c>
       <c r="C49" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A49,'Video Data'!$K$5:$K$71)</f>
-        <v>3879</v>
+        <f aca="false">SUMIF('Video Data'!$AG$5:$AG$71,A49,'Video Data'!$K$5:$K$71)</f>
+        <v>6849</v>
       </c>
       <c r="D49" s="37" t="n">
         <f aca="false">IFERROR(C49/B49,0)</f>
-        <v>352.636363636364</v>
+        <v>297.782608695652</v>
       </c>
       <c r="E49" s="46" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A49,'Video Data'!$L$5:$L$71)</f>
-        <v>22.6211</v>
+        <f aca="false">SUMIF('Video Data'!$AG$5:$AG$71,A49,'Video Data'!$L$5:$L$71)</f>
+        <v>18.6493</v>
       </c>
       <c r="F49" s="46" t="n">
         <f aca="false">IFERROR(E49*3600/C49,0)</f>
-        <v>20.994060324826</v>
+        <v>9.80252299605782</v>
       </c>
       <c r="G49" s="52" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A49,'Video Data'!$O$5:$O$71)/C49*1000,0)</f>
-        <v>0.773395204949729</v>
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AG$5:$AG$71,A49,'Video Data'!$O$5:$O$71)/C49*1000,0)</f>
+        <v>0.14600671630895</v>
       </c>
       <c r="H49" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A49,'Video Data'!$Q$5:$Q$71)</f>
-        <v>15196</v>
+        <f aca="false">SUMIF('Video Data'!$AG$5:$AG$71,A49,'Video Data'!$Q$5:$Q$71)</f>
+        <v>12328</v>
       </c>
       <c r="I49" s="53" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A49,'Video Data'!$S$5:$S$71)/H49,0)</f>
-        <v>0.0492892866543827</v>
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AG$5:$AG$71,A49,'Video Data'!$S$5:$S$71)/H49,0)</f>
+        <v>0.0303374432186892</v>
       </c>
       <c r="J49" s="36" t="str">
         <f aca="false">IF(B49&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="61" t="s">
-        <v>304</v>
-      </c>
-      <c r="B50" s="35" t="n">
-        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A50)</f>
-        <v>2</v>
-      </c>
-      <c r="C50" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A50,'Video Data'!$K$5:$K$71)</f>
-        <v>138</v>
-      </c>
-      <c r="D50" s="37" t="n">
-        <f aca="false">IFERROR(C50/B50,0)</f>
-        <v>69</v>
-      </c>
-      <c r="E50" s="46" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A50,'Video Data'!$L$5:$L$71)</f>
-        <v>0.4289</v>
-      </c>
-      <c r="F50" s="46" t="n">
-        <f aca="false">IFERROR(E50*3600/C50,0)</f>
-        <v>11.1886956521739</v>
-      </c>
-      <c r="G50" s="52" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A50,'Video Data'!$O$5:$O$71)/C50*1000,0)</f>
-        <v>7.2463768115942</v>
-      </c>
-      <c r="H50" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A50,'Video Data'!$Q$5:$Q$71)</f>
-        <v>930</v>
-      </c>
-      <c r="I50" s="53" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A50,'Video Data'!$S$5:$S$71)/H50,0)</f>
-        <v>0.0236559139784946</v>
-      </c>
-      <c r="J50" s="36" t="str">
-        <f aca="false">IF(B50&lt;5,"⚠ small sample","OK")</f>
-        <v>⚠ small sample</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="61" t="s">
-        <v>305</v>
-      </c>
-      <c r="B51" s="35" t="n">
-        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A51)</f>
-        <v>2</v>
-      </c>
-      <c r="C51" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A51,'Video Data'!$K$5:$K$71)</f>
-        <v>373</v>
-      </c>
-      <c r="D51" s="37" t="n">
-        <f aca="false">IFERROR(C51/B51,0)</f>
-        <v>186.5</v>
-      </c>
-      <c r="E51" s="46" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A51,'Video Data'!$L$5:$L$71)</f>
-        <v>1.2229</v>
-      </c>
-      <c r="F51" s="46" t="n">
-        <f aca="false">IFERROR(E51*3600/C51,0)</f>
-        <v>11.8027882037534</v>
-      </c>
-      <c r="G51" s="52" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A51,'Video Data'!$O$5:$O$71)/C51*1000,0)</f>
-        <v>2.68096514745308</v>
-      </c>
-      <c r="H51" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A51,'Video Data'!$Q$5:$Q$71)</f>
-        <v>1261</v>
-      </c>
-      <c r="I51" s="53" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A51,'Video Data'!$S$5:$S$71)/H51,0)</f>
-        <v>0.0126883425852498</v>
-      </c>
-      <c r="J51" s="36" t="str">
-        <f aca="false">IF(B51&lt;5,"⚠ small sample","OK")</f>
-        <v>⚠ small sample</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="61" t="s">
-        <v>306</v>
-      </c>
-      <c r="B52" s="35" t="n">
-        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A52)</f>
-        <v>12</v>
-      </c>
-      <c r="C52" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A52,'Video Data'!$K$5:$K$71)</f>
-        <v>4204</v>
-      </c>
-      <c r="D52" s="37" t="n">
-        <f aca="false">IFERROR(C52/B52,0)</f>
-        <v>350.333333333333</v>
-      </c>
-      <c r="E52" s="46" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A52,'Video Data'!$L$5:$L$71)</f>
-        <v>8.0529</v>
-      </c>
-      <c r="F52" s="46" t="n">
-        <f aca="false">IFERROR(E52*3600/C52,0)</f>
-        <v>6.89591817316841</v>
-      </c>
-      <c r="G52" s="52" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A52,'Video Data'!$O$5:$O$71)/C52*1000,0)</f>
-        <v>1.18934348239772</v>
-      </c>
-      <c r="H52" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A52,'Video Data'!$Q$5:$Q$71)</f>
-        <v>22046</v>
-      </c>
-      <c r="I52" s="53" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A52,'Video Data'!$S$5:$S$71)/H52,0)</f>
-        <v>0.0255375124739182</v>
-      </c>
-      <c r="J52" s="36" t="str">
-        <f aca="false">IF(B52&lt;5,"⚠ small sample","OK")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="61" t="s">
-        <v>307</v>
-      </c>
-      <c r="B53" s="35" t="n">
-        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A53)</f>
-        <v>16</v>
-      </c>
-      <c r="C53" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A53,'Video Data'!$K$5:$K$71)</f>
-        <v>11385</v>
-      </c>
-      <c r="D53" s="37" t="n">
-        <f aca="false">IFERROR(C53/B53,0)</f>
-        <v>711.5625</v>
-      </c>
-      <c r="E53" s="46" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A53,'Video Data'!$L$5:$L$71)</f>
-        <v>18.1698</v>
-      </c>
-      <c r="F53" s="46" t="n">
-        <f aca="false">IFERROR(E53*3600/C53,0)</f>
-        <v>5.74539130434783</v>
-      </c>
-      <c r="G53" s="52" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A53,'Video Data'!$O$5:$O$71)/C53*1000,0)</f>
-        <v>0.790513833992095</v>
-      </c>
-      <c r="H53" s="37" t="n">
-        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A53,'Video Data'!$Q$5:$Q$71)</f>
-        <v>146235</v>
-      </c>
-      <c r="I53" s="53" t="n">
-        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A53,'Video Data'!$S$5:$S$71)/H53,0)</f>
-        <v>0.0659828358464116</v>
-      </c>
-      <c r="J53" s="36" t="str">
-        <f aca="false">IF(B53&lt;5,"⚠ small sample","OK")</f>
-        <v>OK</v>
+      <c r="K49" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$AG$5:$AG$71,A49,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$AG$5:$AG$71,A49,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>9.19842312746386</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="B50" s="62"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
+      <c r="J50" s="62"/>
+      <c r="K50" s="62"/>
+    </row>
+    <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="60" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="61" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B54" s="35" t="n">
         <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A54)</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C54" s="37" t="n">
         <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A54,'Video Data'!$K$5:$K$71)</f>
-        <v>5311</v>
+        <v>790</v>
       </c>
       <c r="D54" s="37" t="n">
         <f aca="false">IFERROR(C54/B54,0)</f>
-        <v>331.9375</v>
+        <v>98.75</v>
       </c>
       <c r="E54" s="46" t="n">
         <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A54,'Video Data'!$L$5:$L$71)</f>
-        <v>6.4757</v>
+        <v>7.6445</v>
       </c>
       <c r="F54" s="46" t="n">
         <f aca="false">IFERROR(E54*3600/C54,0)</f>
-        <v>4.38947844097157</v>
+        <v>34.8356962025317</v>
       </c>
       <c r="G54" s="52" t="n">
         <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A54,'Video Data'!$O$5:$O$71)/C54*1000,0)</f>
-        <v>0</v>
+        <v>1.26582278481013</v>
       </c>
       <c r="H54" s="37" t="n">
         <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A54,'Video Data'!$Q$5:$Q$71)</f>
-        <v>2651</v>
+        <v>8549</v>
       </c>
       <c r="I54" s="53" t="n">
         <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A54,'Video Data'!$S$5:$S$71)/H54,0)</f>
-        <v>0.036589966050547</v>
+        <v>0.0426950520528717</v>
       </c>
       <c r="J54" s="36" t="str">
         <f aca="false">IF(B54&lt;5,"⚠ small sample","OK")</f>
         <v>OK</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="62" t="s">
-        <v>309</v>
-      </c>
-      <c r="B55" s="62"/>
-      <c r="C55" s="62"/>
-      <c r="D55" s="62"/>
-      <c r="E55" s="62"/>
-      <c r="F55" s="62"/>
-      <c r="G55" s="62"/>
-      <c r="H55" s="62"/>
-      <c r="I55" s="62"/>
-      <c r="J55" s="62"/>
+      <c r="K54" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A54,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$F$5:$F$71,A54,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>13.0434782608696</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="61" t="s">
+        <v>312</v>
+      </c>
+      <c r="B55" s="35" t="n">
+        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A55)</f>
+        <v>11</v>
+      </c>
+      <c r="C55" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A55,'Video Data'!$K$5:$K$71)</f>
+        <v>3879</v>
+      </c>
+      <c r="D55" s="37" t="n">
+        <f aca="false">IFERROR(C55/B55,0)</f>
+        <v>352.636363636364</v>
+      </c>
+      <c r="E55" s="46" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A55,'Video Data'!$L$5:$L$71)</f>
+        <v>22.6211</v>
+      </c>
+      <c r="F55" s="46" t="n">
+        <f aca="false">IFERROR(E55*3600/C55,0)</f>
+        <v>20.994060324826</v>
+      </c>
+      <c r="G55" s="52" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A55,'Video Data'!$O$5:$O$71)/C55*1000,0)</f>
+        <v>0.773395204949729</v>
+      </c>
+      <c r="H55" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A55,'Video Data'!$Q$5:$Q$71)</f>
+        <v>15196</v>
+      </c>
+      <c r="I55" s="53" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A55,'Video Data'!$S$5:$S$71)/H55,0)</f>
+        <v>0.0492892866543827</v>
+      </c>
+      <c r="J55" s="36" t="str">
+        <f aca="false">IF(B55&lt;5,"⚠ small sample","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="K55" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A55,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$F$5:$F$71,A55,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>15.2149106124002</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="61" t="s">
+        <v>313</v>
+      </c>
+      <c r="B56" s="35" t="n">
+        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A56)</f>
+        <v>2</v>
+      </c>
+      <c r="C56" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A56,'Video Data'!$K$5:$K$71)</f>
+        <v>138</v>
+      </c>
+      <c r="D56" s="37" t="n">
+        <f aca="false">IFERROR(C56/B56,0)</f>
+        <v>69</v>
+      </c>
+      <c r="E56" s="46" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A56,'Video Data'!$L$5:$L$71)</f>
+        <v>0.4289</v>
+      </c>
+      <c r="F56" s="46" t="n">
+        <f aca="false">IFERROR(E56*3600/C56,0)</f>
+        <v>11.1886956521739</v>
+      </c>
+      <c r="G56" s="52" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A56,'Video Data'!$O$5:$O$71)/C56*1000,0)</f>
+        <v>7.2463768115942</v>
+      </c>
+      <c r="H56" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A56,'Video Data'!$Q$5:$Q$71)</f>
+        <v>930</v>
+      </c>
+      <c r="I56" s="53" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A56,'Video Data'!$S$5:$S$71)/H56,0)</f>
+        <v>0.0236559139784946</v>
+      </c>
+      <c r="J56" s="36" t="str">
+        <f aca="false">IF(B56&lt;5,"⚠ small sample","OK")</f>
+        <v>⚠ small sample</v>
+      </c>
+      <c r="K56" s="46" t="str">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A56,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$F$5:$F$71,A56,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>n/a</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="61" t="s">
+        <v>314</v>
+      </c>
+      <c r="B57" s="35" t="n">
+        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A57)</f>
+        <v>2</v>
+      </c>
+      <c r="C57" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A57,'Video Data'!$K$5:$K$71)</f>
+        <v>373</v>
+      </c>
+      <c r="D57" s="37" t="n">
+        <f aca="false">IFERROR(C57/B57,0)</f>
+        <v>186.5</v>
+      </c>
+      <c r="E57" s="46" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A57,'Video Data'!$L$5:$L$71)</f>
+        <v>1.2229</v>
+      </c>
+      <c r="F57" s="46" t="n">
+        <f aca="false">IFERROR(E57*3600/C57,0)</f>
+        <v>11.8027882037534</v>
+      </c>
+      <c r="G57" s="52" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A57,'Video Data'!$O$5:$O$71)/C57*1000,0)</f>
+        <v>2.68096514745308</v>
+      </c>
+      <c r="H57" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A57,'Video Data'!$Q$5:$Q$71)</f>
+        <v>1261</v>
+      </c>
+      <c r="I57" s="53" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A57,'Video Data'!$S$5:$S$71)/H57,0)</f>
+        <v>0.0126883425852498</v>
+      </c>
+      <c r="J57" s="36" t="str">
+        <f aca="false">IF(B57&lt;5,"⚠ small sample","OK")</f>
+        <v>⚠ small sample</v>
+      </c>
+      <c r="K57" s="46" t="str">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A57,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$F$5:$F$71,A57,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>n/a</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="61" t="s">
+        <v>315</v>
+      </c>
+      <c r="B58" s="35" t="n">
+        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A58)</f>
+        <v>12</v>
+      </c>
+      <c r="C58" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A58,'Video Data'!$K$5:$K$71)</f>
+        <v>4204</v>
+      </c>
+      <c r="D58" s="37" t="n">
+        <f aca="false">IFERROR(C58/B58,0)</f>
+        <v>350.333333333333</v>
+      </c>
+      <c r="E58" s="46" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A58,'Video Data'!$L$5:$L$71)</f>
+        <v>8.0529</v>
+      </c>
+      <c r="F58" s="46" t="n">
+        <f aca="false">IFERROR(E58*3600/C58,0)</f>
+        <v>6.89591817316841</v>
+      </c>
+      <c r="G58" s="52" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A58,'Video Data'!$O$5:$O$71)/C58*1000,0)</f>
+        <v>1.18934348239772</v>
+      </c>
+      <c r="H58" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A58,'Video Data'!$Q$5:$Q$71)</f>
+        <v>22046</v>
+      </c>
+      <c r="I58" s="53" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A58,'Video Data'!$S$5:$S$71)/H58,0)</f>
+        <v>0.0255375124739182</v>
+      </c>
+      <c r="J58" s="36" t="str">
+        <f aca="false">IF(B58&lt;5,"⚠ small sample","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="K58" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A58,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$F$5:$F$71,A58,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>8.12347684809098</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="61" t="s">
+        <v>316</v>
+      </c>
+      <c r="B59" s="35" t="n">
+        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A59)</f>
+        <v>16</v>
+      </c>
+      <c r="C59" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A59,'Video Data'!$K$5:$K$71)</f>
+        <v>11385</v>
+      </c>
+      <c r="D59" s="37" t="n">
+        <f aca="false">IFERROR(C59/B59,0)</f>
+        <v>711.5625</v>
+      </c>
+      <c r="E59" s="46" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A59,'Video Data'!$L$5:$L$71)</f>
+        <v>18.1698</v>
+      </c>
+      <c r="F59" s="46" t="n">
+        <f aca="false">IFERROR(E59*3600/C59,0)</f>
+        <v>5.74539130434783</v>
+      </c>
+      <c r="G59" s="52" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A59,'Video Data'!$O$5:$O$71)/C59*1000,0)</f>
+        <v>0.790513833992095</v>
+      </c>
+      <c r="H59" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A59,'Video Data'!$Q$5:$Q$71)</f>
+        <v>146235</v>
+      </c>
+      <c r="I59" s="53" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A59,'Video Data'!$S$5:$S$71)/H59,0)</f>
+        <v>0.0659828358464116</v>
+      </c>
+      <c r="J59" s="36" t="str">
+        <f aca="false">IF(B59&lt;5,"⚠ small sample","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="K59" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A59,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$F$5:$F$71,A59,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>2.75168422051428</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="61" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" s="35" t="n">
+        <f aca="false">COUNTIF('Video Data'!$F$5:$F$71,A60)</f>
+        <v>16</v>
+      </c>
+      <c r="C60" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A60,'Video Data'!$K$5:$K$71)</f>
+        <v>5311</v>
+      </c>
+      <c r="D60" s="37" t="n">
+        <f aca="false">IFERROR(C60/B60,0)</f>
+        <v>331.9375</v>
+      </c>
+      <c r="E60" s="46" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A60,'Video Data'!$L$5:$L$71)</f>
+        <v>6.4757</v>
+      </c>
+      <c r="F60" s="46" t="n">
+        <f aca="false">IFERROR(E60*3600/C60,0)</f>
+        <v>4.38947844097157</v>
+      </c>
+      <c r="G60" s="52" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A60,'Video Data'!$O$5:$O$71)/C60*1000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="37" t="n">
+        <f aca="false">SUMIF('Video Data'!$F$5:$F$71,A60,'Video Data'!$Q$5:$Q$71)</f>
+        <v>2651</v>
+      </c>
+      <c r="I60" s="53" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A60,'Video Data'!$S$5:$S$71)/H60,0)</f>
+        <v>0.036589966050547</v>
+      </c>
+      <c r="J60" s="36" t="str">
+        <f aca="false">IF(B60&lt;5,"⚠ small sample","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="K60" s="46" t="n">
+        <f aca="false">IFERROR(SUMIF('Video Data'!$F$5:$F$71,A60,'Video Data'!$AD$5:$AD$71)/SUMIF('Video Data'!$F$5:$F$71,A60,'Video Data'!$AH$5:$AH$71)*1000,"n/a")</f>
+        <v>3.2032032032032</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="62" t="s">
+        <v>318</v>
+      </c>
+      <c r="B61" s="62"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="62"/>
+      <c r="E61" s="62"/>
+      <c r="F61" s="62"/>
+      <c r="G61" s="62"/>
+      <c r="H61" s="62"/>
+      <c r="I61" s="62"/>
+      <c r="J61" s="62"/>
+      <c r="K61" s="62"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A55:J55"/>
+  <mergeCells count="8">
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="A61:K61"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D7">
     <cfRule type="colorScale" priority="2">
@@ -26406,13 +26853,24 @@
       <formula>AND(ISNUMBER(I6),I6&lt;0.04)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K6:K7">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K6),K6&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K6),AND(K6&gt;=10,K6&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K6),K6&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J6:J7">
-    <cfRule type="cellIs" priority="7" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="10" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12:D13">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -26424,7 +26882,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12:F13">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
@@ -26434,23 +26892,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12:I13">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(I12),I12&gt;=0.06)</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(I12),AND(I12&gt;=0.04,I12&lt;0.06))</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(I12),I12&lt;0.04)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K12:K13">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K12),K12&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K12),AND(K12&gt;=10,K12&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K12),K12&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J12:J13">
-    <cfRule type="cellIs" priority="13" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="19" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:D21">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -26462,7 +26931,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F21">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
@@ -26472,23 +26941,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I21">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(I18),I18&gt;=0.06)</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(I18),AND(I18&gt;=0.04,I18&lt;0.06))</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(I18),I18&lt;0.04)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K18:K21">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K18),K18&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K18),AND(K18&gt;=10,K18&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K18),K18&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J18:J21">
-    <cfRule type="cellIs" priority="19" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="28" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D26:D27">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -26500,7 +26980,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26:F27">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
@@ -26510,23 +26990,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(I26),I26&gt;=0.06)</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(I26),AND(I26&gt;=0.04,I26&lt;0.06))</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(I26),I26&lt;0.04)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K26:K27">
+    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K26),K26&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K26),AND(K26&gt;=10,K26&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K26),K26&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J26:J27">
-    <cfRule type="cellIs" priority="25" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="37" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32:D34">
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -26538,7 +27029,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="colorScale" priority="27">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
@@ -26548,23 +27039,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:I34">
-    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(I32),I32&gt;=0.06)</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(I32),AND(I32&gt;=0.04,I32&lt;0.06))</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(I32),I32&lt;0.04)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K32:K34">
+    <cfRule type="expression" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K32),K32&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K32),AND(K32&gt;=10,K32&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K32),K32&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J32:J34">
-    <cfRule type="cellIs" priority="31" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="46" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:D43">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -26576,7 +27078,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39:F43">
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
@@ -26586,23 +27088,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I39:I43">
-    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="49" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(I39),I39&gt;=0.06)</formula>
     </cfRule>
-    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="50" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(I39),AND(I39&gt;=0.04,I39&lt;0.06))</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="51" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(I39),I39&lt;0.04)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K39:K43">
+    <cfRule type="expression" priority="52" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K39),K39&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="53" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K39),AND(K39&gt;=10,K39&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="54" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K39),K39&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J39:J43">
-    <cfRule type="cellIs" priority="37" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="55" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:D54">
-    <cfRule type="colorScale" priority="38">
+  <conditionalFormatting sqref="D48:D49">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -26613,8 +27126,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F48:F54">
-    <cfRule type="colorScale" priority="39">
+  <conditionalFormatting sqref="F48:F49">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
@@ -26623,19 +27136,79 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I48:I54">
-    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="I48:I49">
+    <cfRule type="expression" priority="58" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(I48),I48&gt;=0.06)</formula>
     </cfRule>
-    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="59" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(I48),AND(I48&gt;=0.04,I48&lt;0.06))</formula>
     </cfRule>
-    <cfRule type="expression" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="60" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(I48),I48&lt;0.04)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:J54">
-    <cfRule type="cellIs" priority="43" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+  <conditionalFormatting sqref="K48:K49">
+    <cfRule type="expression" priority="61" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K48),K48&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="62" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K48),AND(K48&gt;=10,K48&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K48),K48&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:J49">
+    <cfRule type="cellIs" priority="64" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D54:D60">
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F54:F60">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I54:I60">
+    <cfRule type="expression" priority="67" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(I54),I54&gt;=0.06)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="68" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(I54),AND(I54&gt;=0.04,I54&lt;0.06))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="69" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(I54),I54&lt;0.04)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K54:K60">
+    <cfRule type="expression" priority="70" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K54),K54&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="71" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K54),AND(K54&gt;=10,K54&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="72" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K54),K54&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J54:J60">
+    <cfRule type="cellIs" priority="73" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26668,29 +27241,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26782,7 +27355,7 @@
         <v>532.166666666667</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27036,7 +27609,7 @@
         <v>–</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27056,7 +27629,7 @@
         <v>–</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27418,7 +27991,7 @@
         <v>367.769230769231</v>
       </c>
       <c r="E44" s="36" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27546,7 +28119,7 @@
         <v>471.6</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27566,7 +28139,7 @@
         <v>10.6666666666667</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27625,26 +28198,26 @@
     </row>
     <row r="58" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="60" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="61" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B60" s="37" t="n">
         <f aca="false">SUMPRODUCT((YEAR($A$5:$A$55)=2022)*$B$5:$B$55)</f>
@@ -27661,7 +28234,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="61" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B61" s="37" t="n">
         <f aca="false">SUMPRODUCT((YEAR($A$5:$A$55)=2023)*$B$5:$B$55)</f>
@@ -27678,7 +28251,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="61" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B62" s="37" t="n">
         <f aca="false">SUMPRODUCT((YEAR($A$5:$A$55)=2024)*$B$5:$B$55)</f>
@@ -27695,7 +28268,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="61" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B63" s="37" t="n">
         <f aca="false">SUMPRODUCT((YEAR($A$5:$A$55)=2025)*$B$5:$B$55)</f>
@@ -27712,7 +28285,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="61" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B64" s="37" t="n">
         <f aca="false">SUMPRODUCT((YEAR($A$5:$A$55)=2026)*$B$5:$B$55)</f>
@@ -27729,7 +28302,7 @@
     </row>
     <row r="66" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="62" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B66" s="62"/>
       <c r="C66" s="62"/>
@@ -27749,7 +28322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88F69980-3B35-45C7-814E-FFB14098E7B5}</x14:id>
+          <x14:id>{EDA53586-5863-4EC3-9FA9-B4E79B842425}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -27774,7 +28347,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{88F69980-3B35-45C7-814E-FFB14098E7B5}">
+          <x14:cfRule type="dataBar" id="{EDA53586-5863-4EC3-9FA9-B4E79B842425}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -27813,46 +28386,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="42" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B5" s="64" t="n">
         <v>45248</v>
@@ -27881,7 +28454,7 @@
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="42" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B6" s="64" t="n">
         <v>45989</v>
@@ -27910,7 +28483,7 @@
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="42" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B7" s="64" t="n">
         <v>44901</v>
@@ -27939,7 +28512,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B8" s="64" t="n">
         <v>45970</v>
@@ -27968,7 +28541,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="42" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B9" s="64" t="n">
         <v>46187</v>
@@ -27997,7 +28570,7 @@
     </row>
     <row r="11" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="62" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="62"/>
@@ -28010,15 +28583,15 @@
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="60" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28210,7 +28783,7 @@
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AH74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -28238,63 +28811,65 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E4" s="65" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="M4" s="65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="65" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="P4" s="65" t="s">
         <v>54</v>
@@ -28306,37 +28881,52 @@
         <v>73</v>
       </c>
       <c r="S4" s="65" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="T4" s="65" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="U4" s="65" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="X4" s="65" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="Y4" s="65" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="Z4" s="65" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="AA4" s="65" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="AB4" s="65" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="AC4" s="65" t="s">
-        <v>369</v>
+        <v>378</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="AE4" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="AH4" s="65" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28344,10 +28934,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="D5" s="64" t="n">
         <v>45248</v>
@@ -28361,13 +28951,13 @@
         <v>Sat</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H5" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J5" s="36" t="n">
         <v>3</v>
@@ -28415,7 +29005,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X5" s="36" t="n">
         <f aca="false">LEN(C5)</f>
@@ -28441,16 +29031,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B5,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD5" s="37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE5" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD5),IFERROR(AD5/K5*1000,0),"n/a")</f>
+        <v>2.67162272040887</v>
+      </c>
+      <c r="AF5" s="35" t="n">
+        <v>691</v>
+      </c>
+      <c r="AG5" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH5" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD5),K5,0)</f>
+        <v>8609</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="67" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="C6" s="67" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D6" s="68" t="n">
         <v>45989</v>
@@ -28464,13 +29071,13 @@
         <v>Fri</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H6" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J6" s="67" t="n">
         <v>5</v>
@@ -28518,7 +29125,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="67" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X6" s="67" t="n">
         <f aca="false">LEN(C6)</f>
@@ -28544,16 +29151,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B6,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD6" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD6),IFERROR(AD6/K6*1000,0),"n/a")</f>
+        <v>0.498504486540379</v>
+      </c>
+      <c r="AF6" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH6" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD6),K6,0)</f>
+        <v>2006</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="36" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D7" s="64" t="n">
         <v>44901</v>
@@ -28567,13 +29191,13 @@
         <v>Tue</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J7" s="36" t="n">
         <v>57</v>
@@ -28621,7 +29245,7 @@
         <v>3</v>
       </c>
       <c r="W7" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X7" s="36" t="n">
         <f aca="false">LEN(C7)</f>
@@ -28647,16 +29271,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B7,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD7" s="37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE7" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD7),IFERROR(AD7/K7*1000,0),"n/a")</f>
+        <v>14.3480973175296</v>
+      </c>
+      <c r="AF7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH7" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD7),K7,0)</f>
+        <v>1603</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="67" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C8" s="67" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="D8" s="68" t="n">
         <v>45970</v>
@@ -28670,13 +29311,13 @@
         <v>Sun</v>
       </c>
       <c r="G8" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H8" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I8" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J8" s="67" t="n">
         <v>11</v>
@@ -28724,7 +29365,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X8" s="67" t="n">
         <f aca="false">LEN(C8)</f>
@@ -28750,16 +29391,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B8,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD8" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE8" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD8),IFERROR(AD8/K8*1000,0),"n/a")</f>
+        <v>3.15457413249211</v>
+      </c>
+      <c r="AF8" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH8" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD8),K8,0)</f>
+        <v>1585</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D9" s="64" t="n">
         <v>46187</v>
@@ -28773,13 +29431,13 @@
         <v>Sun</v>
       </c>
       <c r="G9" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H9" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I9" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J9" s="36" t="n">
         <v>4</v>
@@ -28827,7 +29485,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X9" s="36" t="n">
         <f aca="false">LEN(C9)</f>
@@ -28853,16 +29511,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B9,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD9" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD9),IFERROR(AD9/K9*1000,0),"n/a")</f>
+        <v>0.656598818122127</v>
+      </c>
+      <c r="AF9" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH9" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD9),K9,0)</f>
+        <v>1523</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="67" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="67" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="C10" s="67" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="D10" s="68" t="n">
         <v>46151</v>
@@ -28876,13 +29551,13 @@
         <v>Sat</v>
       </c>
       <c r="G10" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H10" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I10" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J10" s="67" t="n">
         <v>4</v>
@@ -28930,7 +29605,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X10" s="67" t="n">
         <f aca="false">LEN(C10)</f>
@@ -28956,16 +29631,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B10,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD10" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD10),IFERROR(AD10/K10*1000,0),"n/a")</f>
+        <v>1.50262960180316</v>
+      </c>
+      <c r="AF10" s="69" t="n">
+        <v>35</v>
+      </c>
+      <c r="AG10" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH10" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD10),K10,0)</f>
+        <v>1331</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="D11" s="64" t="n">
         <v>44817</v>
@@ -28979,13 +29671,13 @@
         <v>Tue</v>
       </c>
       <c r="G11" s="36" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H11" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J11" s="36" t="n">
         <v>211</v>
@@ -29033,7 +29725,7 @@
         <v>0</v>
       </c>
       <c r="W11" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X11" s="36" t="n">
         <f aca="false">LEN(C11)</f>
@@ -29059,16 +29751,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B11,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD11" s="37"/>
+      <c r="AE11" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD11),IFERROR(AD11/K11*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF11" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG11" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH11" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD11),K11,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="67" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="67" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C12" s="67" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="D12" s="68" t="n">
         <v>44897</v>
@@ -29082,13 +29789,13 @@
         <v>Fri</v>
       </c>
       <c r="G12" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H12" s="67" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I12" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J12" s="67" t="n">
         <v>35</v>
@@ -29136,7 +29843,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X12" s="67" t="n">
         <f aca="false">LEN(C12)</f>
@@ -29162,16 +29869,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B12,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD12" s="70" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE12" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD12),IFERROR(AD12/K12*1000,0),"n/a")</f>
+        <v>15.4043645699615</v>
+      </c>
+      <c r="AF12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH12" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD12),K12,0)</f>
+        <v>779</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="36" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="D13" s="64" t="n">
         <v>46138</v>
@@ -29185,13 +29909,13 @@
         <v>Sun</v>
       </c>
       <c r="G13" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J13" s="36" t="n">
         <v>83</v>
@@ -29239,7 +29963,7 @@
         <v>2</v>
       </c>
       <c r="W13" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X13" s="36" t="n">
         <f aca="false">LEN(C13)</f>
@@ -29265,16 +29989,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B13,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD13" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE13" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD13),IFERROR(AD13/K13*1000,0),"n/a")</f>
+        <v>8.34492350486787</v>
+      </c>
+      <c r="AF13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH13" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD13),K13,0)</f>
+        <v>719</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="67" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="C14" s="67" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="D14" s="68" t="n">
         <v>44873</v>
@@ -29288,13 +30029,13 @@
         <v>Tue</v>
       </c>
       <c r="G14" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H14" s="67" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I14" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J14" s="67" t="n">
         <v>50</v>
@@ -29342,7 +30083,7 @@
         <v>6</v>
       </c>
       <c r="W14" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X14" s="67" t="n">
         <f aca="false">LEN(C14)</f>
@@ -29368,16 +30109,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B14,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD14" s="70" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD14),IFERROR(AD14/K14*1000,0),"n/a")</f>
+        <v>23.9043824701195</v>
+      </c>
+      <c r="AF14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH14" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD14),K14,0)</f>
+        <v>502</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="36" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="D15" s="64" t="n">
         <v>46172</v>
@@ -29391,13 +30149,13 @@
         <v>Sat</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J15" s="36" t="n">
         <v>85</v>
@@ -29445,7 +30203,7 @@
         <v>0</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X15" s="36" t="n">
         <f aca="false">LEN(C15)</f>
@@ -29471,16 +30229,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B15,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD15" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD15),IFERROR(AD15/K15*1000,0),"n/a")</f>
+        <v>6.80272108843537</v>
+      </c>
+      <c r="AF15" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG15" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH15" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD15),K15,0)</f>
+        <v>441</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="67" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="67" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C16" s="67" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="D16" s="68" t="n">
         <v>46180</v>
@@ -29494,13 +30269,13 @@
         <v>Sun</v>
       </c>
       <c r="G16" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H16" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I16" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J16" s="67" t="n">
         <v>4</v>
@@ -29548,7 +30323,7 @@
         <v>0</v>
       </c>
       <c r="W16" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X16" s="67" t="n">
         <f aca="false">LEN(C16)</f>
@@ -29574,16 +30349,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B16,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD16" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD16),IFERROR(AD16/K16*1000,0),"n/a")</f>
+        <v>2.91545189504373</v>
+      </c>
+      <c r="AF16" s="69" t="n">
+        <v>53</v>
+      </c>
+      <c r="AG16" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH16" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD16),K16,0)</f>
+        <v>343</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="36" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D17" s="64" t="n">
         <v>45972</v>
@@ -29597,13 +30389,13 @@
         <v>Tue</v>
       </c>
       <c r="G17" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H17" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J17" s="36" t="n">
         <v>5</v>
@@ -29651,7 +30443,7 @@
         <v>1</v>
       </c>
       <c r="W17" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X17" s="36" t="n">
         <f aca="false">LEN(C17)</f>
@@ -29677,16 +30469,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B17,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD17" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD17),IFERROR(AD17/K17*1000,0),"n/a")</f>
+        <v>7.04225352112676</v>
+      </c>
+      <c r="AF17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH17" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD17),K17,0)</f>
+        <v>284</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="67" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="67" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C18" s="67" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D18" s="68" t="n">
         <v>44869</v>
@@ -29700,13 +30509,13 @@
         <v>Fri</v>
       </c>
       <c r="G18" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H18" s="67" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I18" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J18" s="67" t="n">
         <v>61</v>
@@ -29754,7 +30563,7 @@
         <v>6</v>
       </c>
       <c r="W18" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X18" s="67" t="n">
         <f aca="false">LEN(C18)</f>
@@ -29780,16 +30589,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B18,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD18" s="70" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE18" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD18),IFERROR(AD18/K18*1000,0),"n/a")</f>
+        <v>32.1428571428571</v>
+      </c>
+      <c r="AF18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH18" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD18),K18,0)</f>
+        <v>280</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="36" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="D19" s="64" t="n">
         <v>44989</v>
@@ -29803,13 +30629,13 @@
         <v>Sat</v>
       </c>
       <c r="G19" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H19" s="36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J19" s="36" t="n">
         <v>49</v>
@@ -29857,7 +30683,7 @@
         <v>9</v>
       </c>
       <c r="W19" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X19" s="36" t="n">
         <f aca="false">LEN(C19)</f>
@@ -29883,16 +30709,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B19,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD19" s="37"/>
+      <c r="AE19" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD19),IFERROR(AD19/K19*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF19" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG19" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH19" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD19),K19,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="67" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="67" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C20" s="67" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D20" s="68" t="n">
         <v>45982</v>
@@ -29906,13 +30747,13 @@
         <v>Fri</v>
       </c>
       <c r="G20" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H20" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I20" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J20" s="67" t="n">
         <v>5</v>
@@ -29960,7 +30801,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="67" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X20" s="67" t="n">
         <f aca="false">LEN(C20)</f>
@@ -29986,16 +30827,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B20,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD20" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD20),IFERROR(AD20/K20*1000,0),"n/a")</f>
+        <v>3.80228136882129</v>
+      </c>
+      <c r="AF20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH20" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD20),K20,0)</f>
+        <v>263</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="36" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="D21" s="64" t="n">
         <v>45222</v>
@@ -30009,13 +30867,13 @@
         <v>Mon</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J21" s="36" t="n">
         <v>418</v>
@@ -30063,7 +30921,7 @@
         <v>8</v>
       </c>
       <c r="W21" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X21" s="36" t="n">
         <f aca="false">LEN(C21)</f>
@@ -30089,16 +30947,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B21,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD21" s="37"/>
+      <c r="AE21" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD21),IFERROR(AD21/K21*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF21" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG21" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH21" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD21),K21,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="67" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="67" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C22" s="67" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="D22" s="68" t="n">
         <v>45977</v>
@@ -30112,13 +30985,13 @@
         <v>Sun</v>
       </c>
       <c r="G22" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H22" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I22" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J22" s="67" t="n">
         <v>14</v>
@@ -30166,7 +31039,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="67" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X22" s="67" t="n">
         <f aca="false">LEN(C22)</f>
@@ -30192,16 +31065,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B22,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD22" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD22),IFERROR(AD22/K22*1000,0),"n/a")</f>
+        <v>8.03212851405622</v>
+      </c>
+      <c r="AF22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH22" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD22),K22,0)</f>
+        <v>249</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="36" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D23" s="64" t="n">
         <v>44925</v>
@@ -30215,13 +31105,13 @@
         <v>Fri</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H23" s="36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J23" s="36" t="n">
         <v>7</v>
@@ -30269,7 +31159,7 @@
         <v>7</v>
       </c>
       <c r="W23" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X23" s="36" t="n">
         <f aca="false">LEN(C23)</f>
@@ -30295,16 +31185,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B23,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD23" s="37"/>
+      <c r="AE23" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD23),IFERROR(AD23/K23*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF23" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG23" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH23" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD23),K23,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="67" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="67" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C24" s="67" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D24" s="68" t="n">
         <v>45979</v>
@@ -30318,13 +31223,13 @@
         <v>Tue</v>
       </c>
       <c r="G24" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H24" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I24" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J24" s="67" t="n">
         <v>6</v>
@@ -30372,7 +31277,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X24" s="67" t="n">
         <f aca="false">LEN(C24)</f>
@@ -30398,16 +31303,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B24,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD24" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE24" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD24),IFERROR(AD24/K24*1000,0),"n/a")</f>
+        <v>8.92857142857143</v>
+      </c>
+      <c r="AF24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH24" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD24),K24,0)</f>
+        <v>224</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="36" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="D25" s="64" t="n">
         <v>44945</v>
@@ -30421,13 +31343,13 @@
         <v>Thu</v>
       </c>
       <c r="G25" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H25" s="36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J25" s="36" t="n">
         <v>60</v>
@@ -30475,7 +31397,7 @@
         <v>7</v>
       </c>
       <c r="W25" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X25" s="36" t="n">
         <f aca="false">LEN(C25)</f>
@@ -30501,16 +31423,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B25,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD25" s="37"/>
+      <c r="AE25" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD25),IFERROR(AD25/K25*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF25" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG25" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH25" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD25),K25,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="67" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C26" s="67" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="D26" s="68" t="n">
         <v>45064</v>
@@ -30524,13 +31461,13 @@
         <v>Thu</v>
       </c>
       <c r="G26" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H26" s="67" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I26" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J26" s="67" t="n">
         <v>8</v>
@@ -30578,7 +31515,7 @@
         <v>7</v>
       </c>
       <c r="W26" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X26" s="67" t="n">
         <f aca="false">LEN(C26)</f>
@@ -30604,16 +31541,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B26,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD26" s="70"/>
+      <c r="AE26" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD26),IFERROR(AD26/K26*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF26" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG26" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH26" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD26),K26,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="36" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="D27" s="64" t="n">
         <v>45290</v>
@@ -30627,13 +31579,13 @@
         <v>Sat</v>
       </c>
       <c r="G27" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H27" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I27" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J27" s="36" t="n">
         <v>79</v>
@@ -30681,7 +31633,7 @@
         <v>6</v>
       </c>
       <c r="W27" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X27" s="36" t="n">
         <f aca="false">LEN(C27)</f>
@@ -30707,16 +31659,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B27,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD27" s="37"/>
+      <c r="AE27" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD27),IFERROR(AD27/K27*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF27" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG27" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH27" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD27),K27,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="67" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="67" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="D28" s="68" t="n">
         <v>44907</v>
@@ -30730,13 +31697,13 @@
         <v>Mon</v>
       </c>
       <c r="G28" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H28" s="67" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I28" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J28" s="67" t="n">
         <v>33</v>
@@ -30784,7 +31751,7 @@
         <v>3</v>
       </c>
       <c r="W28" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X28" s="67" t="n">
         <f aca="false">LEN(C28)</f>
@@ -30810,16 +31777,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B28,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD28" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE28" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD28),IFERROR(AD28/K28*1000,0),"n/a")</f>
+        <v>12.1212121212121</v>
+      </c>
+      <c r="AF28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH28" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD28),K28,0)</f>
+        <v>165</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="36" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D29" s="64" t="n">
         <v>45296</v>
@@ -30833,13 +31817,13 @@
         <v>Fri</v>
       </c>
       <c r="G29" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H29" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I29" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J29" s="36" t="n">
         <v>11</v>
@@ -30887,7 +31871,7 @@
         <v>6</v>
       </c>
       <c r="W29" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X29" s="36" t="n">
         <f aca="false">LEN(C29)</f>
@@ -30913,16 +31897,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B29,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD29" s="37"/>
+      <c r="AE29" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD29),IFERROR(AD29/K29*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF29" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG29" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH29" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD29),K29,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="67" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="67" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="C30" s="67" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D30" s="68" t="n">
         <v>44890</v>
@@ -30936,13 +31935,13 @@
         <v>Fri</v>
       </c>
       <c r="G30" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H30" s="67" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="I30" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J30" s="67" t="n">
         <v>11</v>
@@ -30990,7 +31989,7 @@
         <v>3</v>
       </c>
       <c r="W30" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X30" s="67" t="n">
         <f aca="false">LEN(C30)</f>
@@ -31016,16 +32015,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B30,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD30" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE30" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD30),IFERROR(AD30/K30*1000,0),"n/a")</f>
+        <v>39.4736842105263</v>
+      </c>
+      <c r="AF30" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH30" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD30),K30,0)</f>
+        <v>152</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="36" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="D31" s="64" t="n">
         <v>46194</v>
@@ -31039,13 +32055,13 @@
         <v>Sun</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J31" s="36" t="n">
         <v>5</v>
@@ -31093,7 +32109,7 @@
         <v>0</v>
       </c>
       <c r="W31" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X31" s="36" t="n">
         <f aca="false">LEN(C31)</f>
@@ -31119,16 +32135,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B31,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD31" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD31),IFERROR(AD31/K31*1000,0),"n/a")</f>
+        <v>6.75675675675676</v>
+      </c>
+      <c r="AF31" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG31" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH31" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD31),K31,0)</f>
+        <v>148</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="67" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="C32" s="67" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D32" s="68" t="n">
         <v>45024</v>
@@ -31142,13 +32175,13 @@
         <v>Sat</v>
       </c>
       <c r="G32" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H32" s="67" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I32" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J32" s="67" t="n">
         <v>61</v>
@@ -31196,7 +32229,7 @@
         <v>11</v>
       </c>
       <c r="W32" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X32" s="67" t="n">
         <f aca="false">LEN(C32)</f>
@@ -31222,16 +32255,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B32,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD32" s="70"/>
+      <c r="AE32" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD32),IFERROR(AD32/K32*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF32" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG32" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH32" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD32),K32,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="36" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="D33" s="64" t="n">
         <v>45570</v>
@@ -31245,13 +32293,13 @@
         <v>Sat</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J33" s="36" t="n">
         <v>1663</v>
@@ -31299,7 +32347,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X33" s="36" t="n">
         <f aca="false">LEN(C33)</f>
@@ -31325,16 +32373,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B33,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD33" s="37"/>
+      <c r="AE33" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD33),IFERROR(AD33/K33*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF33" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG33" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH33" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD33),K33,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="n">
         <v>30</v>
       </c>
       <c r="B34" s="67" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="C34" s="67" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="D34" s="68" t="n">
         <v>44915</v>
@@ -31348,13 +32411,13 @@
         <v>Tue</v>
       </c>
       <c r="G34" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H34" s="67" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I34" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J34" s="67" t="n">
         <v>32</v>
@@ -31402,7 +32465,7 @@
         <v>5</v>
       </c>
       <c r="W34" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X34" s="67" t="n">
         <f aca="false">LEN(C34)</f>
@@ -31428,16 +32491,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B34,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD34" s="70"/>
+      <c r="AE34" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD34),IFERROR(AD34/K34*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF34" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG34" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH34" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD34),K34,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="36" t="n">
         <v>31</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="D35" s="64" t="n">
         <v>45062</v>
@@ -31451,13 +32529,13 @@
         <v>Tue</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H35" s="36" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I35" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J35" s="36" t="n">
         <v>10</v>
@@ -31505,7 +32583,7 @@
         <v>7</v>
       </c>
       <c r="W35" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X35" s="36" t="n">
         <f aca="false">LEN(C35)</f>
@@ -31531,16 +32609,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B35,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD35" s="37"/>
+      <c r="AE35" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD35),IFERROR(AD35/K35*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF35" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG35" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH35" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD35),K35,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="67" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="67" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="C36" s="67" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="D36" s="68" t="n">
         <v>44955</v>
@@ -31554,13 +32647,13 @@
         <v>Sun</v>
       </c>
       <c r="G36" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H36" s="67" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I36" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J36" s="67" t="n">
         <v>32</v>
@@ -31608,7 +32701,7 @@
         <v>10</v>
       </c>
       <c r="W36" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X36" s="67" t="n">
         <f aca="false">LEN(C36)</f>
@@ -31634,16 +32727,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B36,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD36" s="70"/>
+      <c r="AE36" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD36),IFERROR(AD36/K36*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF36" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG36" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH36" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD36),K36,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="36" t="n">
         <v>33</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D37" s="64" t="n">
         <v>44911</v>
@@ -31657,13 +32765,13 @@
         <v>Fri</v>
       </c>
       <c r="G37" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H37" s="36" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="I37" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J37" s="36" t="n">
         <v>11</v>
@@ -31711,7 +32819,7 @@
         <v>7</v>
       </c>
       <c r="W37" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X37" s="36" t="n">
         <f aca="false">LEN(C37)</f>
@@ -31737,16 +32845,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B37,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD37" s="37"/>
+      <c r="AE37" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD37),IFERROR(AD37/K37*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF37" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG37" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH37" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD37),K37,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="67" t="n">
         <v>34</v>
       </c>
       <c r="B38" s="67" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="D38" s="68" t="n">
         <v>44997</v>
@@ -31760,13 +32883,13 @@
         <v>Sun</v>
       </c>
       <c r="G38" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H38" s="67" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="I38" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J38" s="67" t="n">
         <v>24</v>
@@ -31814,7 +32937,7 @@
         <v>9</v>
       </c>
       <c r="W38" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X38" s="67" t="n">
         <f aca="false">LEN(C38)</f>
@@ -31840,16 +32963,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B38,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD38" s="70"/>
+      <c r="AE38" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD38),IFERROR(AD38/K38*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF38" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG38" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH38" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD38),K38,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="36" t="n">
         <v>35</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="D39" s="64" t="n">
         <v>45021</v>
@@ -31863,13 +33001,13 @@
         <v>Wed</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H39" s="36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J39" s="36" t="n">
         <v>11</v>
@@ -31917,7 +33055,7 @@
         <v>11</v>
       </c>
       <c r="W39" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X39" s="36" t="n">
         <f aca="false">LEN(C39)</f>
@@ -31943,16 +33081,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B39,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD39" s="37"/>
+      <c r="AE39" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD39),IFERROR(AD39/K39*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF39" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG39" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH39" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD39),K39,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="67" t="n">
         <v>36</v>
       </c>
       <c r="B40" s="67" t="s">
+        <v>448</v>
+      </c>
+      <c r="C40" s="67" t="s">
         <v>434</v>
-      </c>
-      <c r="C40" s="67" t="s">
-        <v>420</v>
       </c>
       <c r="D40" s="68" t="n">
         <v>45019</v>
@@ -31966,13 +33119,13 @@
         <v>Mon</v>
       </c>
       <c r="G40" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H40" s="67" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I40" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J40" s="67" t="n">
         <v>32</v>
@@ -32020,7 +33173,7 @@
         <v>11</v>
       </c>
       <c r="W40" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X40" s="67" t="n">
         <f aca="false">LEN(C40)</f>
@@ -32046,16 +33199,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B40,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD40" s="70"/>
+      <c r="AE40" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD40),IFERROR(AD40/K40*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF40" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG40" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH40" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD40),K40,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="36" t="n">
         <v>37</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="D41" s="64" t="n">
         <v>45984</v>
@@ -32069,13 +33237,13 @@
         <v>Sun</v>
       </c>
       <c r="G41" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H41" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I41" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J41" s="36" t="n">
         <v>8</v>
@@ -32123,7 +33291,7 @@
         <v>0</v>
       </c>
       <c r="W41" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X41" s="36" t="n">
         <f aca="false">LEN(C41)</f>
@@ -32149,16 +33317,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B41,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD41" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD41),IFERROR(AD41/K41*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH41" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD41),K41,0)</f>
+        <v>122</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="67" t="n">
         <v>38</v>
       </c>
       <c r="B42" s="67" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="C42" s="67" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="D42" s="68" t="n">
         <v>46136</v>
@@ -32172,13 +33357,13 @@
         <v>Fri</v>
       </c>
       <c r="G42" s="67" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H42" s="67" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I42" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J42" s="67" t="n">
         <v>291</v>
@@ -32226,7 +33411,7 @@
         <v>0</v>
       </c>
       <c r="W42" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X42" s="67" t="n">
         <f aca="false">LEN(C42)</f>
@@ -32252,16 +33437,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B42,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD42" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD42),IFERROR(AD42/K42*1000,0),"n/a")</f>
+        <v>8.47457627118644</v>
+      </c>
+      <c r="AF42" s="69" t="n">
+        <v>351</v>
+      </c>
+      <c r="AG42" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH42" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD42),K42,0)</f>
+        <v>118</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="36" t="n">
         <v>39</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="D43" s="64" t="n">
         <v>45963</v>
@@ -32275,13 +33477,13 @@
         <v>Sun</v>
       </c>
       <c r="G43" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H43" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J43" s="36" t="n">
         <v>4</v>
@@ -32329,7 +33531,7 @@
         <v>7</v>
       </c>
       <c r="W43" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X43" s="36" t="n">
         <f aca="false">LEN(C43)</f>
@@ -32355,16 +33557,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B43,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD43" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD43),IFERROR(AD43/K43*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF43" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH43" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD43),K43,0)</f>
+        <v>112</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="67" t="n">
         <v>40</v>
       </c>
       <c r="B44" s="67" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C44" s="67" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="D44" s="68" t="n">
         <v>44956</v>
@@ -32378,13 +33597,13 @@
         <v>Mon</v>
       </c>
       <c r="G44" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H44" s="67" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I44" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J44" s="67" t="n">
         <v>60</v>
@@ -32432,7 +33651,7 @@
         <v>10</v>
       </c>
       <c r="W44" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X44" s="67" t="n">
         <f aca="false">LEN(C44)</f>
@@ -32458,16 +33677,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B44,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD44" s="70"/>
+      <c r="AE44" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD44),IFERROR(AD44/K44*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF44" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG44" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH44" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD44),K44,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="36" t="n">
         <v>41</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="D45" s="64" t="n">
         <v>44947</v>
@@ -32481,13 +33715,13 @@
         <v>Sat</v>
       </c>
       <c r="G45" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H45" s="36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I45" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J45" s="36" t="n">
         <v>61</v>
@@ -32535,7 +33769,7 @@
         <v>9</v>
       </c>
       <c r="W45" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X45" s="36" t="n">
         <f aca="false">LEN(C45)</f>
@@ -32561,16 +33795,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B45,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD45" s="37"/>
+      <c r="AE45" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD45),IFERROR(AD45/K45*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF45" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG45" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH45" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD45),K45,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="67" t="n">
         <v>42</v>
       </c>
       <c r="B46" s="67" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C46" s="67" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D46" s="68" t="n">
         <v>46201</v>
@@ -32584,13 +33833,13 @@
         <v>Sun</v>
       </c>
       <c r="G46" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H46" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I46" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J46" s="67" t="n">
         <v>4</v>
@@ -32638,7 +33887,7 @@
         <v>0</v>
       </c>
       <c r="W46" s="67" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X46" s="67" t="n">
         <f aca="false">LEN(C46)</f>
@@ -32664,16 +33913,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B46,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD46" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD46),IFERROR(AD46/K46*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF46" s="69" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG46" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH46" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD46),K46,0)</f>
+        <v>80</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="36" t="n">
         <v>43</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="D47" s="64" t="n">
         <v>45304</v>
@@ -32687,13 +33953,13 @@
         <v>Sat</v>
       </c>
       <c r="G47" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H47" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I47" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J47" s="36" t="n">
         <v>4</v>
@@ -32741,7 +34007,7 @@
         <v>8</v>
       </c>
       <c r="W47" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X47" s="36" t="n">
         <f aca="false">LEN(C47)</f>
@@ -32767,16 +34033,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B47,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD47" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD47),IFERROR(AD47/K47*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH47" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD47),K47,0)</f>
+        <v>72</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="67" t="n">
         <v>44</v>
       </c>
       <c r="B48" s="67" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="C48" s="67" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D48" s="68" t="n">
         <v>45243</v>
@@ -32790,13 +34073,13 @@
         <v>Mon</v>
       </c>
       <c r="G48" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H48" s="67" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I48" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J48" s="67" t="n">
         <v>13</v>
@@ -32844,7 +34127,7 @@
         <v>8</v>
       </c>
       <c r="W48" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X48" s="67" t="n">
         <f aca="false">LEN(C48)</f>
@@ -32870,16 +34153,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B48,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD48" s="70"/>
+      <c r="AE48" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD48),IFERROR(AD48/K48*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF48" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG48" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH48" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD48),K48,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="36" t="n">
         <v>45</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="D49" s="64" t="n">
         <v>45221</v>
@@ -32893,13 +34191,13 @@
         <v>Sun</v>
       </c>
       <c r="G49" s="36" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H49" s="36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J49" s="36" t="n">
         <v>1388</v>
@@ -32947,7 +34245,7 @@
         <v>10</v>
       </c>
       <c r="W49" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X49" s="36" t="n">
         <f aca="false">LEN(C49)</f>
@@ -32973,16 +34271,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B49,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD49" s="37"/>
+      <c r="AE49" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD49),IFERROR(AD49/K49*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF49" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG49" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH49" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD49),K49,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="67" t="n">
         <v>46</v>
       </c>
       <c r="B50" s="67" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="C50" s="67" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="D50" s="68" t="n">
         <v>45991</v>
@@ -32996,13 +34309,13 @@
         <v>Sun</v>
       </c>
       <c r="G50" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H50" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I50" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J50" s="67" t="n">
         <v>5</v>
@@ -33050,7 +34363,7 @@
         <v>0</v>
       </c>
       <c r="W50" s="67" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X50" s="67" t="n">
         <f aca="false">LEN(C50)</f>
@@ -33076,16 +34389,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B50,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD50" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD50),IFERROR(AD50/K50*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF50" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH50" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD50),K50,0)</f>
+        <v>56</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="36" t="n">
         <v>47</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="D51" s="64" t="n">
         <v>45975</v>
@@ -33099,13 +34429,13 @@
         <v>Fri</v>
       </c>
       <c r="G51" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H51" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J51" s="36" t="n">
         <v>5</v>
@@ -33153,7 +34483,7 @@
         <v>0</v>
       </c>
       <c r="W51" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X51" s="36" t="n">
         <f aca="false">LEN(C51)</f>
@@ -33179,16 +34509,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B51,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD51" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD51),IFERROR(AD51/K51*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH51" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD51),K51,0)</f>
+        <v>48</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="67" t="n">
         <v>48</v>
       </c>
       <c r="B52" s="67" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="C52" s="67" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="D52" s="68" t="n">
         <v>45237</v>
@@ -33202,13 +34549,13 @@
         <v>Tue</v>
       </c>
       <c r="G52" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H52" s="67" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I52" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J52" s="67" t="n">
         <v>10</v>
@@ -33256,7 +34603,7 @@
         <v>7</v>
       </c>
       <c r="W52" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X52" s="67" t="n">
         <f aca="false">LEN(C52)</f>
@@ -33282,16 +34629,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B52,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD52" s="70"/>
+      <c r="AE52" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD52),IFERROR(AD52/K52*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF52" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG52" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH52" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD52),K52,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="36" t="n">
         <v>49</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="D53" s="64" t="n">
         <v>46173</v>
@@ -33305,13 +34667,13 @@
         <v>Sun</v>
       </c>
       <c r="G53" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H53" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J53" s="36" t="n">
         <v>54</v>
@@ -33359,7 +34721,7 @@
         <v>0</v>
       </c>
       <c r="W53" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X53" s="36" t="n">
         <f aca="false">LEN(C53)</f>
@@ -33385,16 +34747,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B53,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD53" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD53),IFERROR(AD53/K53*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH53" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD53),K53,0)</f>
+        <v>43</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="67" t="n">
         <v>50</v>
       </c>
       <c r="B54" s="67" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="C54" s="67" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="D54" s="68" t="n">
         <v>45439</v>
@@ -33408,13 +34787,13 @@
         <v>Mon</v>
       </c>
       <c r="G54" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H54" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I54" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J54" s="67" t="n">
         <v>4</v>
@@ -33462,7 +34841,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X54" s="67" t="n">
         <f aca="false">LEN(C54)</f>
@@ -33488,16 +34867,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B54,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD54" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE54" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD54),IFERROR(AD54/K54*1000,0),"n/a")</f>
+        <v>24.390243902439</v>
+      </c>
+      <c r="AF54" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH54" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD54),K54,0)</f>
+        <v>41</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="36" t="n">
         <v>51</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="D55" s="64" t="n">
         <v>45241</v>
@@ -33511,13 +34907,13 @@
         <v>Sat</v>
       </c>
       <c r="G55" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H55" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I55" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J55" s="36" t="n">
         <v>4</v>
@@ -33565,7 +34961,7 @@
         <v>0</v>
       </c>
       <c r="W55" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X55" s="36" t="n">
         <f aca="false">LEN(C55)</f>
@@ -33591,16 +34987,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B55,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD55" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD55),IFERROR(AD55/K55*1000,0),"n/a")</f>
+        <v>25.6410256410256</v>
+      </c>
+      <c r="AF55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH55" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD55),K55,0)</f>
+        <v>39</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="67" t="n">
         <v>52</v>
       </c>
       <c r="B56" s="67" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="C56" s="67" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="D56" s="68" t="n">
         <v>45219</v>
@@ -33614,13 +35027,13 @@
         <v>Fri</v>
       </c>
       <c r="G56" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H56" s="67" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I56" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J56" s="67" t="n">
         <v>8</v>
@@ -33668,7 +35081,7 @@
         <v>11</v>
       </c>
       <c r="W56" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X56" s="67" t="n">
         <f aca="false">LEN(C56)</f>
@@ -33694,16 +35107,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B56,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD56" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD56),IFERROR(AD56/K56*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF56" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH56" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD56),K56,0)</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="36" t="n">
         <v>53</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="D57" s="64" t="n">
         <v>45432</v>
@@ -33717,13 +35147,13 @@
         <v>Mon</v>
       </c>
       <c r="G57" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H57" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I57" s="36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J57" s="36" t="n">
         <v>8</v>
@@ -33771,7 +35201,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X57" s="36" t="n">
         <f aca="false">LEN(C57)</f>
@@ -33797,16 +35227,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B57,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD57" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD57),IFERROR(AD57/K57*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH57" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD57),K57,0)</f>
+        <v>24</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="67" t="n">
         <v>54</v>
       </c>
       <c r="B58" s="67" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="C58" s="67" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="D58" s="68" t="n">
         <v>46158</v>
@@ -33820,13 +35267,13 @@
         <v>Sat</v>
       </c>
       <c r="G58" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H58" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I58" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J58" s="67" t="n">
         <v>4</v>
@@ -33874,7 +35321,7 @@
         <v>1</v>
       </c>
       <c r="W58" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X58" s="67" t="n">
         <f aca="false">LEN(C58)</f>
@@ -33900,16 +35347,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B58,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD58" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD58),IFERROR(AD58/K58*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF58" s="69" t="n">
+        <v>35</v>
+      </c>
+      <c r="AG58" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH58" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD58),K58,0)</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="36" t="n">
         <v>55</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="D59" s="64" t="n">
         <v>45968</v>
@@ -33923,13 +35387,13 @@
         <v>Fri</v>
       </c>
       <c r="G59" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H59" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I59" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J59" s="36" t="n">
         <v>4</v>
@@ -33977,7 +35441,7 @@
         <v>5</v>
       </c>
       <c r="W59" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X59" s="36" t="n">
         <f aca="false">LEN(C59)</f>
@@ -34003,16 +35467,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B59,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD59" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD59),IFERROR(AD59/K59*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF59" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH59" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD59),K59,0)</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="67" t="n">
         <v>56</v>
       </c>
       <c r="B60" s="67" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="C60" s="67" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="D60" s="68" t="n">
         <v>45319</v>
@@ -34026,13 +35507,13 @@
         <v>Sun</v>
       </c>
       <c r="G60" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H60" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I60" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J60" s="67" t="n">
         <v>9</v>
@@ -34080,7 +35561,7 @@
         <v>8</v>
       </c>
       <c r="W60" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X60" s="67" t="n">
         <f aca="false">LEN(C60)</f>
@@ -34106,16 +35587,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B60,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD60" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD60),IFERROR(AD60/K60*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF60" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH60" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD60),K60,0)</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="36" t="n">
         <v>57</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="D61" s="64" t="n">
         <v>46137</v>
@@ -34129,13 +35627,13 @@
         <v>Sat</v>
       </c>
       <c r="G61" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H61" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I61" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J61" s="36" t="n">
         <v>61</v>
@@ -34183,7 +35681,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X61" s="36" t="n">
         <f aca="false">LEN(C61)</f>
@@ -34209,16 +35707,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B61,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD61" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD61),IFERROR(AD61/K61*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF61" s="35" t="n">
+        <v>147</v>
+      </c>
+      <c r="AG61" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH61" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD61),K61,0)</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="67" t="n">
         <v>58</v>
       </c>
       <c r="B62" s="67" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="C62" s="67" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="D62" s="68" t="n">
         <v>45245</v>
@@ -34232,13 +35747,13 @@
         <v>Wed</v>
       </c>
       <c r="G62" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H62" s="67" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I62" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J62" s="67" t="n">
         <v>2</v>
@@ -34286,7 +35801,7 @@
         <v>8</v>
       </c>
       <c r="W62" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X62" s="67" t="n">
         <f aca="false">LEN(C62)</f>
@@ -34312,16 +35827,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B62,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD62" s="70"/>
+      <c r="AE62" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD62),IFERROR(AD62/K62*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF62" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG62" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH62" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD62),K62,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="36" t="n">
         <v>59</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="D63" s="64" t="n">
         <v>45965</v>
@@ -34335,13 +35865,13 @@
         <v>Tue</v>
       </c>
       <c r="G63" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H63" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I63" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J63" s="36" t="n">
         <v>2</v>
@@ -34389,7 +35919,7 @@
         <v>8</v>
       </c>
       <c r="W63" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X63" s="36" t="n">
         <f aca="false">LEN(C63)</f>
@@ -34415,16 +35945,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B63,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD63" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD63),IFERROR(AD63/K63*1000,0),"n/a")</f>
+        <v>100</v>
+      </c>
+      <c r="AF63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH63" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD63),K63,0)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="67" t="n">
         <v>60</v>
       </c>
       <c r="B64" s="67" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="C64" s="67" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="D64" s="68" t="n">
         <v>46165</v>
@@ -34438,13 +35985,13 @@
         <v>Sat</v>
       </c>
       <c r="G64" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H64" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I64" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J64" s="67" t="n">
         <v>3</v>
@@ -34492,7 +36039,7 @@
         <v>1</v>
       </c>
       <c r="W64" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X64" s="67" t="n">
         <f aca="false">LEN(C64)</f>
@@ -34518,16 +36065,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B64,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD64" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD64),IFERROR(AD64/K64*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF64" s="69" t="n">
+        <v>35</v>
+      </c>
+      <c r="AG64" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH64" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD64),K64,0)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="36" t="n">
         <v>61</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="D65" s="64" t="n">
         <v>45986</v>
@@ -34541,13 +36105,13 @@
         <v>Tue</v>
       </c>
       <c r="G65" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H65" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I65" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J65" s="36" t="n">
         <v>3</v>
@@ -34595,7 +36159,7 @@
         <v>0</v>
       </c>
       <c r="W65" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X65" s="36" t="n">
         <f aca="false">LEN(C65)</f>
@@ -34621,16 +36185,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B65,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD65" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD65),IFERROR(AD65/K65*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH65" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD65),K65,0)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="67" t="n">
         <v>62</v>
       </c>
       <c r="B66" s="67" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="C66" s="67" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="D66" s="68" t="n">
         <v>46179</v>
@@ -34644,13 +36225,13 @@
         <v>Sat</v>
       </c>
       <c r="G66" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H66" s="67" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I66" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J66" s="67" t="n">
         <v>9</v>
@@ -34698,7 +36279,7 @@
         <v>0</v>
       </c>
       <c r="W66" s="67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X66" s="67" t="n">
         <f aca="false">LEN(C66)</f>
@@ -34724,16 +36305,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B66,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD66" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD66),IFERROR(AD66/K66*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF66" s="69" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG66" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH66" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD66),K66,0)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="36" t="n">
         <v>63</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="C67" s="36" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="D67" s="64" t="n">
         <v>46214</v>
@@ -34747,13 +36345,13 @@
         <v>Sat</v>
       </c>
       <c r="G67" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H67" s="36" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J67" s="36" t="n">
         <v>3</v>
@@ -34801,7 +36399,7 @@
         <v>0</v>
       </c>
       <c r="W67" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X67" s="36" t="n">
         <f aca="false">LEN(C67)</f>
@@ -34827,16 +36425,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B67,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD67" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD67),IFERROR(AD67/K67*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF67" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG67" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH67" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD67),K67,0)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="67" t="n">
         <v>64</v>
       </c>
       <c r="B68" s="67" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C68" s="67" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="D68" s="68" t="n">
         <v>46208</v>
@@ -34850,13 +36465,13 @@
         <v>Sun</v>
       </c>
       <c r="G68" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H68" s="67" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I68" s="67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J68" s="67" t="n">
         <v>2</v>
@@ -34904,7 +36519,7 @@
         <v>0</v>
       </c>
       <c r="W68" s="67" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X68" s="67" t="n">
         <f aca="false">LEN(C68)</f>
@@ -34930,16 +36545,33 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B68,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD68" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="72" t="n">
+        <f aca="false">IF(ISNUMBER(AD68),IFERROR(AD68/K68*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF68" s="69" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG68" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH68" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD68),K68,0)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="36" t="n">
         <v>65</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="C69" s="36" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="D69" s="64" t="n">
         <v>45993</v>
@@ -34953,13 +36585,13 @@
         <v>Tue</v>
       </c>
       <c r="G69" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H69" s="36" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J69" s="36" t="n">
         <v>5</v>
@@ -35005,7 +36637,7 @@
         <v>0</v>
       </c>
       <c r="W69" s="36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="X69" s="36" t="n">
         <f aca="false">LEN(C69)</f>
@@ -35031,16 +36663,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B69,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD69" s="37"/>
+      <c r="AE69" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(AD69),IFERROR(AD69/K69*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF69" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG69" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH69" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD69),K69,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="67" t="n">
         <v>66</v>
       </c>
       <c r="B70" s="67" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="C70" s="67" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="D70" s="68" t="n">
         <v>45446</v>
@@ -35054,13 +36701,13 @@
         <v>Mon</v>
       </c>
       <c r="G70" s="67" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H70" s="67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I70" s="67" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J70" s="67" t="n">
         <v>2</v>
@@ -35108,7 +36755,7 @@
         <v>6</v>
       </c>
       <c r="W70" s="67" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X70" s="67" t="n">
         <f aca="false">LEN(C70)</f>
@@ -35134,16 +36781,31 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B70,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD70" s="70"/>
+      <c r="AE70" s="72" t="str">
+        <f aca="false">IF(ISNUMBER(AD70),IFERROR(AD70/K70*1000,0),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="AF70" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="AG70" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH70" s="70" t="n">
+        <f aca="false">IF(ISNUMBER(AD70),K70,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="36" t="n">
         <v>67</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="C71" s="36" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="D71" s="64" t="n">
         <v>46207</v>
@@ -35157,13 +36819,13 @@
         <v>Sat</v>
       </c>
       <c r="G71" s="36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H71" s="36" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J71" s="36" t="n">
         <v>3</v>
@@ -35211,7 +36873,7 @@
         <v>0</v>
       </c>
       <c r="W71" s="36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X71" s="36" t="n">
         <f aca="false">LEN(C71)</f>
@@ -35237,10 +36899,27 @@
         <f aca="false">HYPERLINK("https://youtu.be/"&amp;B71,"▶ Watch")</f>
         <v>▶ Watch</v>
       </c>
+      <c r="AD71" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(AD71),IFERROR(AD71/K71*1000,0),"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="AF71" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG71" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH71" s="37" t="n">
+        <f aca="false">IF(ISNUMBER(AD71),K71,0)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C73" s="15" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="K73" s="55" t="n">
         <f aca="false">SUM(K5:K71)</f>
@@ -35282,14 +36961,22 @@
         <f aca="false">IFERROR(T73/K73,0)</f>
         <v>0.560544478527607</v>
       </c>
+      <c r="AD73" s="55" t="n">
+        <f aca="false">SUM(AD5:AD71)</f>
+        <v>118</v>
+      </c>
+      <c r="AE73" s="57" t="n">
+        <f aca="false">IFERROR(AD73/SUM(AH5:AH71)*1000,0)</f>
+        <v>5.34275106402246</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C74" s="77" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AC71"/>
+  <autoFilter ref="A4:AH71"/>
   <conditionalFormatting sqref="K5:K71">
     <cfRule type="dataBar" priority="2">
       <dataBar showValue="1" minLength="10" maxLength="90">
@@ -35299,7 +36986,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20E0362E-31A7-42D2-A6B8-8BFD1C7452D4}</x14:id>
+          <x14:id>{A17C401F-11D9-433B-A3EA-BAF4AD40D697}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -35313,7 +37000,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4985C0C5-E3C6-4468-8127-7D7810BCD470}</x14:id>
+          <x14:id>{D38A2035-546F-4DB0-A392-EEC674F04A35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -35386,6 +37073,17 @@
       <formula>"Long-form"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AE5:AE71">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(AE5),AE5&gt;=20)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(AE5),AND(AE5&gt;=10,AE5&lt;20))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(AE5),AE5&lt;10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -35399,7 +37097,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20E0362E-31A7-42D2-A6B8-8BFD1C7452D4}">
+          <x14:cfRule type="dataBar" id="{A17C401F-11D9-433B-A3EA-BAF4AD40D697}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -35410,7 +37108,7 @@
           <xm:sqref>K5:K71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4985C0C5-E3C6-4468-8127-7D7810BCD470}">
+          <x14:cfRule type="dataBar" id="{D38A2035-546F-4DB0-A392-EEC674F04A35}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -35432,7 +37130,7 @@
     <tabColor rgb="FF375623"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -35444,32 +37142,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35477,19 +37175,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="F5" s="78" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35497,19 +37195,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="F6" s="78" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35517,19 +37215,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="F7" s="78" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35537,19 +37235,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="F8" s="78" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35557,19 +37255,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="F9" s="78" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35577,19 +37275,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="F10" s="78" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35597,19 +37295,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="F11" s="78" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35617,19 +37315,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="F12" s="78" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35637,19 +37335,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="F13" s="78" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35657,19 +37355,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="F14" s="78" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35677,19 +37375,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="F15" s="78" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35697,19 +37395,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="F16" s="78" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35717,19 +37415,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="42" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="F17" s="78" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35737,23 +37435,43 @@
         <v>14</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="F18" s="78" t="s">
-        <v>570</v>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="F19" s="78" t="s">
+        <v>589</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E18">
+  <conditionalFormatting sqref="E5:E19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEFT(E5,4)="High"</formula>
     </cfRule>
